--- a/files/九龙-长沙湾-连方I.xlsx
+++ b/files/九龙-长沙湾-连方I.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="连方I 销控表" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -111,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -176,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -192,48 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -905,7 +769,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -1001,7 +865,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-14</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1297,7 +1161,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1343,7 +1207,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1389,7 +1253,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1435,7 +1299,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1481,7 +1345,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1669,7 +1533,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -1715,7 +1579,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -1761,7 +1625,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -1807,7 +1671,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -1853,7 +1717,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2037,7 +1901,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2083,7 +1947,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2129,7 +1993,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-23</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2175,7 +2039,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2221,7 +2085,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2359,7 +2223,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -2405,7 +2269,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -2451,7 +2315,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -2497,7 +2361,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-23</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -2543,7 +2407,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-26</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -2589,7 +2453,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -2727,7 +2591,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -2773,7 +2637,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -2819,7 +2683,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -2865,7 +2729,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -2911,7 +2775,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -2957,7 +2821,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -3003,7 +2867,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3049,7 +2913,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -3095,7 +2959,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -3141,7 +3005,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -3187,7 +3051,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -3233,7 +3097,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -3279,7 +3143,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-02</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -3325,7 +3189,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -3371,7 +3235,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -3417,7 +3281,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -3463,7 +3327,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -3509,7 +3373,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-02</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -3555,7 +3419,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -3601,7 +3465,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -3647,7 +3511,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -3693,7 +3557,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -3739,7 +3603,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -3785,7 +3649,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -3831,7 +3695,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -3877,7 +3741,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-03-26</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -3923,7 +3787,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -3969,7 +3833,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -4015,7 +3879,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -4061,7 +3925,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-05</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -4107,7 +3971,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -4153,7 +4017,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -4199,7 +4063,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -4245,7 +4109,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -4291,7 +4155,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -4337,7 +4201,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -4383,7 +4247,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -4429,7 +4293,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -4475,7 +4339,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -4521,7 +4385,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -4567,7 +4431,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -4613,7 +4477,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -4659,7 +4523,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -4705,7 +4569,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-02</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -4751,7 +4615,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -4797,7 +4661,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -4843,7 +4707,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-19</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -4889,7 +4753,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -4935,7 +4799,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -4981,7 +4845,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -5027,7 +4891,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -5073,7 +4937,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -5119,7 +4983,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -5165,7 +5029,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -5211,7 +5075,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -5257,7 +5121,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -5303,7 +5167,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -5349,7 +5213,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-12-01</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -5395,7 +5259,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-05</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -5441,7 +5305,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -5487,7 +5351,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -5533,7 +5397,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -5579,7 +5443,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -5625,7 +5489,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-23</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -5671,7 +5535,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -5717,7 +5581,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-12-12</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -5809,7 +5673,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -5855,7 +5719,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-14</t>
         </is>
       </c>
       <c r="H114" s="5" t="n">
@@ -5901,7 +5765,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-03-25</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
@@ -5947,7 +5811,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -5993,7 +5857,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -6039,7 +5903,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -6085,7 +5949,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-11-29</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -6131,7 +5995,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -6177,7 +6041,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-03-26</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -6223,7 +6087,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-02</t>
         </is>
       </c>
       <c r="H122" s="5" t="n">
@@ -6269,7 +6133,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -6315,7 +6179,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
@@ -6361,7 +6225,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -6407,7 +6271,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="H126" s="5" t="n">
@@ -6453,7 +6317,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-02-21</t>
         </is>
       </c>
       <c r="H127" s="5" t="n">
@@ -6499,7 +6363,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -6545,7 +6409,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-07-13</t>
         </is>
       </c>
       <c r="H129" s="5" t="n">
@@ -6637,7 +6501,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-03-27</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -6683,7 +6547,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
@@ -6729,7 +6593,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="H133" s="5" t="n">
@@ -6775,7 +6639,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
@@ -6821,7 +6685,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-11-29</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -6867,7 +6731,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-02-13</t>
         </is>
       </c>
       <c r="H136" s="5" t="n">
@@ -6913,7 +6777,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="H137" s="5" t="n">
@@ -7005,7 +6869,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="H139" s="5" t="n">
@@ -7051,7 +6915,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-03-26</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -7097,7 +6961,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
@@ -7143,7 +7007,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="H142" s="5" t="n">
@@ -7189,7 +7053,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-02-23</t>
         </is>
       </c>
       <c r="H143" s="5" t="n">
@@ -7235,7 +7099,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="H144" s="5" t="n">
@@ -7281,7 +7145,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-07-05</t>
         </is>
       </c>
       <c r="H145" s="5" t="n">
@@ -7327,7 +7191,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="H146" s="5" t="n">
@@ -7419,7 +7283,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
@@ -7465,7 +7329,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="H149" s="5" t="n">
@@ -7511,7 +7375,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="H150" s="5" t="n">
@@ -7557,7 +7421,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-12-04</t>
         </is>
       </c>
       <c r="H151" s="5" t="n">
@@ -7603,7 +7467,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
@@ -7649,7 +7513,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-03-26</t>
         </is>
       </c>
       <c r="H153" s="5" t="n">
@@ -7695,7 +7559,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-11-29</t>
         </is>
       </c>
       <c r="H154" s="5" t="n">
@@ -7741,7 +7605,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
@@ -7787,7 +7651,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="H156" s="5" t="n">
@@ -7833,7 +7697,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="H157" s="5" t="n">
@@ -7879,7 +7743,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-03-23</t>
         </is>
       </c>
       <c r="H158" s="5" t="n">
@@ -7925,7 +7789,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="H159" s="5" t="n">
@@ -7971,7 +7835,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-11-29</t>
         </is>
       </c>
       <c r="H160" s="5" t="n">
@@ -7993,1572 +7857,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:I26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>连方I - 连方I 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>158 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>10 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>137 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>11 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>27&amp;28/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr"/>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>B | 525呎 (2房)
-$1,150万
-$21,905/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D6" s="18" t="inlineStr">
-        <is>
-          <t>C | 411呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E6" s="18" t="inlineStr">
-        <is>
-          <t>D | 411呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F6" s="18" t="inlineStr">
-        <is>
-          <t>E | 525呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G6" s="16" t="inlineStr"/>
-      <c r="H6" s="16" t="inlineStr"/>
-      <c r="I6" s="16" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>A | 547呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr"/>
-      <c r="D7" s="16" t="inlineStr"/>
-      <c r="E7" s="16" t="inlineStr"/>
-      <c r="F7" s="16" t="inlineStr"/>
-      <c r="G7" s="18" t="inlineStr">
-        <is>
-          <t>F | 439呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H7" s="16" t="inlineStr"/>
-      <c r="I7" s="16" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>A | 231呎 (开放式)
-$478万
-$20,688/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>B | 401呎 (2房)
-$1,088万
-$27,135/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>C | 290呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E8" s="18" t="inlineStr">
-        <is>
-          <t>D | 266呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F8" s="18" t="inlineStr">
-        <is>
-          <t>E | 266呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G8" s="18" t="inlineStr">
-        <is>
-          <t>F | 292呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H8" s="18" t="inlineStr">
-        <is>
-          <t>G | 293呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I8" s="17" t="inlineStr">
-        <is>
-          <t>H | 233呎 (开放式)
-$677万
-$29,039/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>A | 231呎 (开放式)
-$473万
-$20,485/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>B | 401呎 (2房)
-$1,072万
-$26,733/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D9" s="19" t="inlineStr">
-        <is>
-          <t>C | 290呎 (1房)
-$850万
-$29,307/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E9" s="18" t="inlineStr">
-        <is>
-          <t>D | 266呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F9" s="19" t="inlineStr">
-        <is>
-          <t>E | 266呎 (开放式)
-$799万
-$30,026/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G9" s="17" t="inlineStr">
-        <is>
-          <t>F | 292呎 (1房)
-$589万
-$20,168/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H9" s="17" t="inlineStr">
-        <is>
-          <t>G | 293呎 (1房)
-$660万
-$22,536/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I9" s="17" t="inlineStr">
-        <is>
-          <t>H | 233呎 (开放式)
-$458万
-$19,657/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>A | 231呎 (开放式)
-$655万
-$28,368/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>B | 401呎 (2房)
-$1,056万
-$26,337/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D10" s="19" t="inlineStr">
-        <is>
-          <t>C | 290呎 (1房)
-$833万
-$28,734/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E10" s="19" t="inlineStr">
-        <is>
-          <t>D | 266呎 (开放式)
-$783万
-$29,440/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F10" s="19" t="inlineStr">
-        <is>
-          <t>E | 266呎 (开放式)
-$783万
-$29,440/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G10" s="17" t="inlineStr">
-        <is>
-          <t>F | 292呎 (1房)
-$577万
-$19,774/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H10" s="17" t="inlineStr">
-        <is>
-          <t>G | 293呎 (1房)
-$625万
-$21,341/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I10" s="17" t="inlineStr">
-        <is>
-          <t>H | 233呎 (开放式)
-$594万
-$25,511/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>A | 231呎 (开放式)
-$458万
-$19,848/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>B | 401呎 (2房)
-$1,040万
-$25,948/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D11" s="17" t="inlineStr">
-        <is>
-          <t>C | 290呎 (1房)
-$564万
-$19,459/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E11" s="19" t="inlineStr">
-        <is>
-          <t>D | 266呎 (开放式)
-$768万
-$28,861/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F11" s="19" t="inlineStr">
-        <is>
-          <t>E | 266呎 (开放式)
-$768万
-$28,857/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G11" s="17" t="inlineStr">
-        <is>
-          <t>F | 292呎 (1房)
-$792万
-$27,106/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H11" s="17" t="inlineStr">
-        <is>
-          <t>G | 293呎 (1房)
-$905万
-$30,894/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I11" s="17" t="inlineStr">
-        <is>
-          <t>H | 232呎 (开放式)
-$649万
-$27,957/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>A | 231呎 (开放式)
-$454万
-$19,654/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>B | 401呎 (2房)
-$1,025万
-$25,564/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D12" s="17" t="inlineStr">
-        <is>
-          <t>C | 290呎 (1房)
-$559万
-$19,262/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E12" s="19" t="inlineStr">
-        <is>
-          <t>D | 266呎 (开放式)
-$760万
-$28,579/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F12" s="19" t="inlineStr">
-        <is>
-          <t>E | 266呎 (开放式)
-$760万
-$28,575/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G12" s="17" t="inlineStr">
-        <is>
-          <t>F | 292呎 (1房)
-$561万
-$19,209/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H12" s="17" t="inlineStr">
-        <is>
-          <t>G | 293呎 (1房)
-$830万
-$28,321/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I12" s="17" t="inlineStr">
-        <is>
-          <t>H | 233呎 (开放式)
-$642万
-$27,575/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>A | 231呎 (开放式)
-$430万
-$18,615/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>B | 401呎 (2房)
-$1,010万
-$25,187/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D13" s="17" t="inlineStr">
-        <is>
-          <t>C | 290呎 (1房)
-$553万
-$19,072/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E13" s="17" t="inlineStr">
-        <is>
-          <t>D | 266呎 (开放式)
-$602万
-$22,620/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F13" s="17" t="inlineStr">
-        <is>
-          <t>E | 266呎 (开放式)
-$517万
-$19,429/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G13" s="17" t="inlineStr">
-        <is>
-          <t>F | 292呎 (1房)
-$532万
-$18,209/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H13" s="17" t="inlineStr">
-        <is>
-          <t>G | 293呎 (1房)
-$822万
-$28,041/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I13" s="17" t="inlineStr">
-        <is>
-          <t>H | 233呎 (开放式)
-$623万
-$26,751/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>A | 232呎 (开放式)
-$613万
-$26,414/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>B | 401呎 (2房)
-$1,045万
-$26,052/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D14" s="17" t="inlineStr">
-        <is>
-          <t>C | 290呎 (1房)
-$737万
-$25,417/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E14" s="17" t="inlineStr">
-        <is>
-          <t>D | 266呎 (开放式)
-$516万
-$19,410/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F14" s="17" t="inlineStr">
-        <is>
-          <t>E | 266呎 (开放式)
-$514万
-$19,327/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G14" s="17" t="inlineStr">
-        <is>
-          <t>F | 292呎 (1房)
-$772万
-$26,442/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H14" s="17" t="inlineStr">
-        <is>
-          <t>G | 293呎 (1房)
-$789万
-$26,942/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I14" s="17" t="inlineStr">
-        <is>
-          <t>H | 233呎 (开放式)
-$617万
-$26,494/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>A | 232呎 (开放式)
-$445万
-$19,190/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>B | 401呎 (2房)
-$995万
-$24,810/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D15" s="17" t="inlineStr">
-        <is>
-          <t>C | 290呎 (1房)
-$764万
-$26,338/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E15" s="17" t="inlineStr">
-        <is>
-          <t>D | 266呎 (开放式)
-$514万
-$19,323/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F15" s="17" t="inlineStr">
-        <is>
-          <t>E | 266呎 (开放式)
-$718万
-$27,004/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G15" s="17" t="inlineStr">
-        <is>
-          <t>F | 292呎 (1房)
-$551万
-$18,884/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H15" s="17" t="inlineStr">
-        <is>
-          <t>G | 293呎 (1房)
-$782万
-$26,676/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I15" s="17" t="inlineStr">
-        <is>
-          <t>H | 232呎 (开放式)
-$617万
-$26,608/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>A | 232呎 (开放式)
-$594万
-$25,625/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t>B | 401呎 (2房)
-$1,034万
-$25,796/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D16" s="17" t="inlineStr">
-        <is>
-          <t>C | 290呎 (1房)
-$564万
-$19,466/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E16" s="17" t="inlineStr">
-        <is>
-          <t>D | 266呎 (开放式)
-$512万
-$19,229/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F16" s="17" t="inlineStr">
-        <is>
-          <t>E | 266呎 (开放式)
-$704万
-$26,466/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G16" s="17" t="inlineStr">
-        <is>
-          <t>F | 292呎 (1房)
-$763万
-$26,120/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H16" s="17" t="inlineStr">
-        <is>
-          <t>G | 293呎 (1房)
-$774万
-$26,413/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I16" s="17" t="inlineStr">
-        <is>
-          <t>H | 233呎 (开放式)
-$612万
-$26,253/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>A | 232呎 (开放式)
-$588万
-$25,358/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>B | 401呎 (2房)
-$1,040万
-$25,923/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D17" s="17" t="inlineStr">
-        <is>
-          <t>C | 290呎 (1房)
-$753万
-$25,962/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E17" s="17" t="inlineStr">
-        <is>
-          <t>D | 266呎 (开放式)
-$712万
-$26,748/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F17" s="17" t="inlineStr">
-        <is>
-          <t>E | 266呎 (开放式)
-$687万
-$25,838/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G17" s="17" t="inlineStr">
-        <is>
-          <t>F | 292呎 (1房)
-$750万
-$25,695/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H17" s="17" t="inlineStr">
-        <is>
-          <t>G | 293呎 (1房)
-$770万
-$26,273/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I17" s="17" t="inlineStr">
-        <is>
-          <t>H | 232呎 (开放式)
-$606万
-$26,099/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>A | 232呎 (开放式)
-$570万
-$24,569/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C18" s="17" t="inlineStr">
-        <is>
-          <t>B | 401呎 (2房)
-$1,034万
-$25,796/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D18" s="17" t="inlineStr">
-        <is>
-          <t>C | 290呎 (1房)
-$748万
-$25,797/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E18" s="17" t="inlineStr">
-        <is>
-          <t>D | 266呎 (开放式)
-$719万
-$27,034/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F18" s="17" t="inlineStr">
-        <is>
-          <t>E | 266呎 (开放式)
-$682万
-$25,647/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G18" s="17" t="inlineStr">
-        <is>
-          <t>F | 292呎 (1房)
-$719万
-$24,610/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H18" s="17" t="inlineStr">
-        <is>
-          <t>G | 293呎 (1房)
-$766万
-$26,140/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I18" s="17" t="inlineStr">
-        <is>
-          <t>H | 233呎 (开放式)
-$588万
-$25,223/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>A | 232呎 (开放式)
-$538万
-$23,177/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C19" s="17" t="inlineStr">
-        <is>
-          <t>B | 401呎 (2房)
-$805万
-$20,082/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D19" s="17" t="inlineStr">
-        <is>
-          <t>C | 290呎 (1房)
-$746万
-$25,721/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E19" s="17" t="inlineStr">
-        <is>
-          <t>D | 266呎 (开放式)
-$698万
-$26,222/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F19" s="17" t="inlineStr">
-        <is>
-          <t>E | 266呎 (开放式)
-$677万
-$25,447/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G19" s="17" t="inlineStr">
-        <is>
-          <t>F | 292呎 (1房)
-$743万
-$25,452/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H19" s="17" t="inlineStr">
-        <is>
-          <t>G | 293呎 (1房)
-$730万
-$24,918/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I19" s="17" t="inlineStr">
-        <is>
-          <t>H | 232呎 (开放式)
-$577万
-$24,888/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B20" s="19" t="inlineStr">
-        <is>
-          <t>A | 232呎 (开放式)
-$543万
-$23,422/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>B | 401呎 (2房)
-$789万
-$19,678/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D20" s="17" t="inlineStr">
-        <is>
-          <t>C | 290呎 (1房)
-$732万
-$25,228/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E20" s="17" t="inlineStr">
-        <is>
-          <t>D | 266呎 (开放式)
-$691万
-$25,962/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F20" s="17" t="inlineStr">
-        <is>
-          <t>E | 266呎 (开放式)
-$673万
-$25,286/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G20" s="17" t="inlineStr">
-        <is>
-          <t>F | 292呎 (1房)
-$741万
-$25,366/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H20" s="17" t="inlineStr">
-        <is>
-          <t>G | 293呎 (1房)
-$726万
-$24,785/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I20" s="17" t="inlineStr">
-        <is>
-          <t>H | 233呎 (开放式)
-$569万
-$24,429/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>A | 231呎 (开放式)
-$528万
-$22,835/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C21" s="17" t="inlineStr">
-        <is>
-          <t>B | 401呎 (2房)
-$754万
-$18,791/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D21" s="17" t="inlineStr">
-        <is>
-          <t>C | 290呎 (1房)
-$684万
-$23,593/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E21" s="17" t="inlineStr">
-        <is>
-          <t>D | 266呎 (开放式)
-$684万
-$25,703/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F21" s="17" t="inlineStr">
-        <is>
-          <t>E | 266呎 (开放式)
-$510万
-$19,154/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G21" s="17" t="inlineStr">
-        <is>
-          <t>F | 292呎 (1房)
-$694万
-$23,760/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H21" s="17" t="inlineStr">
-        <is>
-          <t>G | 293呎 (1房)
-$703万
-$23,993/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I21" s="17" t="inlineStr">
-        <is>
-          <t>H | 233呎 (开放式)
-$561万
-$24,082/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="inlineStr">
-        <is>
-          <t>A | 231呎 (开放式)
-$459万
-$19,853/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C22" s="17" t="inlineStr">
-        <is>
-          <t>B | 401呎 (2房)
-$885万
-$22,060/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D22" s="17" t="inlineStr">
-        <is>
-          <t>C | 290呎 (1房)
-$673万
-$23,197/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E22" s="17" t="inlineStr">
-        <is>
-          <t>D | 266呎 (开放式)
-$677万
-$25,451/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F22" s="17" t="inlineStr">
-        <is>
-          <t>E | 266呎 (开放式)
-$648万
-$24,361/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G22" s="17" t="inlineStr">
-        <is>
-          <t>F | 292呎 (1房)
-$544万
-$18,616/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H22" s="17" t="inlineStr">
-        <is>
-          <t>G | 293呎 (1房)
-$696万
-$23,768/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I22" s="17" t="inlineStr">
-        <is>
-          <t>H | 233呎 (开放式)
-$560万
-$24,039/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="inlineStr">
-        <is>
-          <t>A | 232呎 (开放式)
-$508万
-$21,914/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C23" s="17" t="inlineStr">
-        <is>
-          <t>B | 401呎 (2房)
-$757万
-$18,870/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D23" s="17" t="inlineStr">
-        <is>
-          <t>C | 290呎 (1房)
-$666万
-$22,983/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E23" s="17" t="inlineStr">
-        <is>
-          <t>D | 266呎 (开放式)
-$674万
-$25,350/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F23" s="17" t="inlineStr">
-        <is>
-          <t>E | 266呎 (开放式)
-$508万
-$19,090/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G23" s="17" t="inlineStr">
-        <is>
-          <t>F | 292呎 (1房)
-$668万
-$22,877/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H23" s="17" t="inlineStr">
-        <is>
-          <t>G | 293呎 (1房)
-$700万
-$23,904/呎
-(24年-03月)</t>
-        </is>
-      </c>
-      <c r="I23" s="17" t="inlineStr">
-        <is>
-          <t>H | 232呎 (开放式)
-$556万
-$23,948/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="inlineStr">
-        <is>
-          <t>A | 231呎 (开放式)
-$443万
-$19,165/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C24" s="17" t="inlineStr">
-        <is>
-          <t>B | 401呎 (2房)
-$860万
-$21,449/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D24" s="17" t="inlineStr">
-        <is>
-          <t>C | 290呎 (1房)
-$656万
-$22,624/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E24" s="17" t="inlineStr">
-        <is>
-          <t>D | 266呎 (开放式)
-$662万
-$24,902/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F24" s="17" t="inlineStr">
-        <is>
-          <t>E | 266呎 (开放式)
-$630万
-$23,699/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G24" s="17" t="inlineStr">
-        <is>
-          <t>F | 292呎 (1房)
-$668万
-$22,860/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H24" s="17" t="inlineStr">
-        <is>
-          <t>G | 293呎 (1房)
-$692万
-$23,621/呎
-(24年-03月)</t>
-        </is>
-      </c>
-      <c r="I24" s="17" t="inlineStr">
-        <is>
-          <t>H | 233呎 (开放式)
-$603万
-$25,897/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="inlineStr">
-        <is>
-          <t>A | 231呎 (开放式)
-$440万
-$19,035/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C25" s="17" t="inlineStr">
-        <is>
-          <t>B | 401呎 (2房)
-$722万
-$18,005/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D25" s="17" t="inlineStr">
-        <is>
-          <t>C | 290呎 (1房)
-$649万
-$22,372/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E25" s="17" t="inlineStr">
-        <is>
-          <t>D | 266呎 (开放式)
-$656万
-$24,654/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F25" s="17" t="inlineStr">
-        <is>
-          <t>E | 266呎 (开放式)
-$472万
-$17,741/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G25" s="17" t="inlineStr">
-        <is>
-          <t>F | 292呎 (1房)
-$670万
-$22,942/呎
-(24年-03月)</t>
-        </is>
-      </c>
-      <c r="H25" s="17" t="inlineStr">
-        <is>
-          <t>G | 293呎 (1房)
-$672万
-$22,942/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I25" s="17" t="inlineStr">
-        <is>
-          <t>H | 232呎 (开放式)
-$537万
-$23,164/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B26" s="17" t="inlineStr">
-        <is>
-          <t>A | 232呎 (开放式)
-$416万
-$17,931/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C26" s="17" t="inlineStr">
-        <is>
-          <t>B | 401呎 (2房)
-$737万
-$18,389/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D26" s="17" t="inlineStr">
-        <is>
-          <t>C | 290呎 (1房)
-$626万
-$21,583/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E26" s="17" t="inlineStr">
-        <is>
-          <t>D | 266呎 (开放式)
-$649万
-$24,414/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F26" s="17" t="inlineStr">
-        <is>
-          <t>E | 266呎 (开放式)
-$659万
-$24,782/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G26" s="17" t="inlineStr">
-        <is>
-          <t>F | 292呎 (1房)
-$686万
-$23,476/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H26" s="17" t="inlineStr">
-        <is>
-          <t>G | 293呎 (1房)
-$559万
-$19,092/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I26" s="17" t="inlineStr">
-        <is>
-          <t>H | 232呎 (开放式)
-$520万
-$22,422/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:I1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/九龙-长沙湾-连方I.xlsx
+++ b/files/九龙-长沙湾-连方I.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="连方I" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +42,96 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +142,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +207,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +223,60 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +653,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -7857,4 +8036,1572 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:I25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>连方I 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>27&amp;28</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr"/>
+      <c r="C5" s="21" t="inlineStr">
+        <is>
+          <t>B | 525呎 (2房)
+$1150万
+$21,905/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="D5" s="22" t="inlineStr">
+        <is>
+          <t>C | 411呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E5" s="22" t="inlineStr">
+        <is>
+          <t>D | 411呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F5" s="22" t="inlineStr">
+        <is>
+          <t>E | 525呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="inlineStr"/>
+      <c r="H5" s="20" t="inlineStr"/>
+      <c r="I5" s="20" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 547呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr"/>
+      <c r="G6" s="22" t="inlineStr">
+        <is>
+          <t>F | 439呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr"/>
+      <c r="I6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>A | 231呎 (开放式)
+$478万
+$20,688/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>B | 401呎 (2房)
+$1088万
+$27,135/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>C | 290呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>D | 266呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F7" s="22" t="inlineStr">
+        <is>
+          <t>E | 266呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G7" s="22" t="inlineStr">
+        <is>
+          <t>F | 292呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H7" s="22" t="inlineStr">
+        <is>
+          <t>G | 293呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I7" s="21" t="inlineStr">
+        <is>
+          <t>H | 233呎 (开放式)
+$677万
+$29,039/呎
+(25年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>A | 231呎 (开放式)
+$473万
+$20,485/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>B | 401呎 (2房)
+$1072万
+$26,733/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>C | 290呎 (1房)
+$850万
+$29,307/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>D | 266呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F8" s="23" t="inlineStr">
+        <is>
+          <t>E | 266呎 (开放式)
+$799万
+$30,026/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G8" s="21" t="inlineStr">
+        <is>
+          <t>F | 292呎 (1房)
+$589万
+$20,168/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H8" s="21" t="inlineStr">
+        <is>
+          <t>G | 293呎 (1房)
+$660万
+$22,536/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="I8" s="21" t="inlineStr">
+        <is>
+          <t>H | 233呎 (开放式)
+$458万
+$19,657/呎
+(25年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>A | 231呎 (开放式)
+$655万
+$28,368/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>B | 401呎 (2房)
+$1056万
+$26,337/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>C | 290呎 (1房)
+$833万
+$28,734/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E9" s="23" t="inlineStr">
+        <is>
+          <t>D | 266呎 (开放式)
+$783万
+$29,440/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F9" s="23" t="inlineStr">
+        <is>
+          <t>E | 266呎 (开放式)
+$783万
+$29,440/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G9" s="21" t="inlineStr">
+        <is>
+          <t>F | 292呎 (1房)
+$577万
+$19,774/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t>G | 293呎 (1房)
+$625万
+$21,341/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="I9" s="21" t="inlineStr">
+        <is>
+          <t>H | 233呎 (开放式)
+$594万
+$25,511/呎
+(25年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>A | 231呎 (开放式)
+$458万
+$19,848/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>B | 401呎 (2房)
+$1040万
+$25,948/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t>C | 290呎 (1房)
+$564万
+$19,459/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E10" s="23" t="inlineStr">
+        <is>
+          <t>D | 266呎 (开放式)
+$768万
+$28,861/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F10" s="23" t="inlineStr">
+        <is>
+          <t>E | 266呎 (开放式)
+$768万
+$28,857/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G10" s="21" t="inlineStr">
+        <is>
+          <t>F | 292呎 (1房)
+$792万
+$27,106/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="H10" s="21" t="inlineStr">
+        <is>
+          <t>G | 293呎 (1房)
+$905万
+$30,894/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="I10" s="21" t="inlineStr">
+        <is>
+          <t>H | 232呎 (开放式)
+$649万
+$27,957/呎
+(24年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>A | 231呎 (开放式)
+$454万
+$19,654/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>B | 401呎 (2房)
+$1025万
+$25,564/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>C | 290呎 (1房)
+$559万
+$19,262/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E11" s="23" t="inlineStr">
+        <is>
+          <t>D | 266呎 (开放式)
+$760万
+$28,579/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F11" s="23" t="inlineStr">
+        <is>
+          <t>E | 266呎 (开放式)
+$760万
+$28,575/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G11" s="21" t="inlineStr">
+        <is>
+          <t>F | 292呎 (1房)
+$561万
+$19,209/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="H11" s="21" t="inlineStr">
+        <is>
+          <t>G | 293呎 (1房)
+$830万
+$28,321/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="I11" s="21" t="inlineStr">
+        <is>
+          <t>H | 233呎 (开放式)
+$642万
+$27,575/呎
+(24年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>A | 231呎 (开放式)
+$430万
+$18,615/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>B | 401呎 (2房)
+$1010万
+$25,187/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>C | 290呎 (1房)
+$553万
+$19,072/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>D | 266呎 (开放式)
+$602万
+$22,620/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t>E | 266呎 (开放式)
+$517万
+$19,429/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="G12" s="21" t="inlineStr">
+        <is>
+          <t>F | 292呎 (1房)
+$532万
+$18,209/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t>G | 293呎 (1房)
+$822万
+$28,041/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="I12" s="21" t="inlineStr">
+        <is>
+          <t>H | 233呎 (开放式)
+$623万
+$26,751/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>A | 232呎 (开放式)
+$613万
+$26,414/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>B | 401呎 (2房)
+$1045万
+$26,052/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t>C | 290呎 (1房)
+$737万
+$25,417/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>D | 266呎 (开放式)
+$516万
+$19,410/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t>E | 266呎 (开放式)
+$514万
+$19,327/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="G13" s="21" t="inlineStr">
+        <is>
+          <t>F | 292呎 (1房)
+$772万
+$26,442/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="H13" s="21" t="inlineStr">
+        <is>
+          <t>G | 293呎 (1房)
+$789万
+$26,942/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="I13" s="21" t="inlineStr">
+        <is>
+          <t>H | 233呎 (开放式)
+$617万
+$26,494/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>A | 232呎 (开放式)
+$445万
+$19,190/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>B | 401呎 (2房)
+$995万
+$24,810/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t>C | 290呎 (1房)
+$764万
+$26,338/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>D | 266呎 (开放式)
+$514万
+$19,323/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="F14" s="21" t="inlineStr">
+        <is>
+          <t>E | 266呎 (开放式)
+$718万
+$27,004/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G14" s="21" t="inlineStr">
+        <is>
+          <t>F | 292呎 (1房)
+$551万
+$18,884/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H14" s="21" t="inlineStr">
+        <is>
+          <t>G | 293呎 (1房)
+$782万
+$26,676/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="I14" s="21" t="inlineStr">
+        <is>
+          <t>H | 232呎 (开放式)
+$617万
+$26,608/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>A | 232呎 (开放式)
+$594万
+$25,625/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>B | 401呎 (2房)
+$1034万
+$25,796/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>C | 290呎 (1房)
+$564万
+$19,466/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E15" s="21" t="inlineStr">
+        <is>
+          <t>D | 266呎 (开放式)
+$512万
+$19,229/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F15" s="21" t="inlineStr">
+        <is>
+          <t>E | 266呎 (开放式)
+$704万
+$26,466/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G15" s="21" t="inlineStr">
+        <is>
+          <t>F | 292呎 (1房)
+$763万
+$26,120/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="H15" s="21" t="inlineStr">
+        <is>
+          <t>G | 293呎 (1房)
+$774万
+$26,413/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="I15" s="21" t="inlineStr">
+        <is>
+          <t>H | 233呎 (开放式)
+$612万
+$26,253/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>A | 232呎 (开放式)
+$588万
+$25,358/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>B | 401呎 (2房)
+$1040万
+$25,923/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="inlineStr">
+        <is>
+          <t>C | 290呎 (1房)
+$753万
+$25,962/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>D | 266呎 (开放式)
+$712万
+$26,748/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="F16" s="21" t="inlineStr">
+        <is>
+          <t>E | 266呎 (开放式)
+$687万
+$25,838/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G16" s="21" t="inlineStr">
+        <is>
+          <t>F | 292呎 (1房)
+$750万
+$25,695/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="H16" s="21" t="inlineStr">
+        <is>
+          <t>G | 293呎 (1房)
+$770万
+$26,273/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="I16" s="21" t="inlineStr">
+        <is>
+          <t>H | 232呎 (开放式)
+$606万
+$26,099/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
+        <is>
+          <t>A | 232呎 (开放式)
+$570万
+$24,569/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="inlineStr">
+        <is>
+          <t>B | 401呎 (2房)
+$1034万
+$25,796/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="inlineStr">
+        <is>
+          <t>C | 290呎 (1房)
+$748万
+$25,797/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="E17" s="21" t="inlineStr">
+        <is>
+          <t>D | 266呎 (开放式)
+$719万
+$27,034/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="F17" s="21" t="inlineStr">
+        <is>
+          <t>E | 266呎 (开放式)
+$682万
+$25,647/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G17" s="21" t="inlineStr">
+        <is>
+          <t>F | 292呎 (1房)
+$719万
+$24,610/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="H17" s="21" t="inlineStr">
+        <is>
+          <t>G | 293呎 (1房)
+$766万
+$26,140/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="I17" s="21" t="inlineStr">
+        <is>
+          <t>H | 233呎 (开放式)
+$588万
+$25,223/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>A | 232呎 (开放式)
+$538万
+$23,177/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="inlineStr">
+        <is>
+          <t>B | 401呎 (2房)
+$805万
+$20,082/呎
+(22年-12月)</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="inlineStr">
+        <is>
+          <t>C | 290呎 (1房)
+$746万
+$25,721/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="E18" s="21" t="inlineStr">
+        <is>
+          <t>D | 266呎 (开放式)
+$698万
+$26,222/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="F18" s="21" t="inlineStr">
+        <is>
+          <t>E | 266呎 (开放式)
+$677万
+$25,447/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G18" s="21" t="inlineStr">
+        <is>
+          <t>F | 292呎 (1房)
+$743万
+$25,452/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="H18" s="21" t="inlineStr">
+        <is>
+          <t>G | 293呎 (1房)
+$730万
+$24,918/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I18" s="21" t="inlineStr">
+        <is>
+          <t>H | 232呎 (开放式)
+$577万
+$24,888/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>A | 232呎 (开放式)
+$543万
+$23,422/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C19" s="21" t="inlineStr">
+        <is>
+          <t>B | 401呎 (2房)
+$789万
+$19,678/呎
+(22年-12月)</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="inlineStr">
+        <is>
+          <t>C | 290呎 (1房)
+$732万
+$25,228/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="E19" s="21" t="inlineStr">
+        <is>
+          <t>D | 266呎 (开放式)
+$691万
+$25,962/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="F19" s="21" t="inlineStr">
+        <is>
+          <t>E | 266呎 (开放式)
+$673万
+$25,286/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G19" s="21" t="inlineStr">
+        <is>
+          <t>F | 292呎 (1房)
+$741万
+$25,366/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="H19" s="21" t="inlineStr">
+        <is>
+          <t>G | 293呎 (1房)
+$726万
+$24,785/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I19" s="21" t="inlineStr">
+        <is>
+          <t>H | 233呎 (开放式)
+$569万
+$24,429/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t>A | 231呎 (开放式)
+$528万
+$22,835/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="inlineStr">
+        <is>
+          <t>B | 401呎 (2房)
+$754万
+$18,791/呎
+(22年-11月)</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="inlineStr">
+        <is>
+          <t>C | 290呎 (1房)
+$684万
+$23,593/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E20" s="21" t="inlineStr">
+        <is>
+          <t>D | 266呎 (开放式)
+$684万
+$25,703/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="F20" s="21" t="inlineStr">
+        <is>
+          <t>E | 266呎 (开放式)
+$510万
+$19,154/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="G20" s="21" t="inlineStr">
+        <is>
+          <t>F | 292呎 (1房)
+$694万
+$23,760/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="H20" s="21" t="inlineStr">
+        <is>
+          <t>G | 293呎 (1房)
+$703万
+$23,993/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I20" s="21" t="inlineStr">
+        <is>
+          <t>H | 233呎 (开放式)
+$561万
+$24,082/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
+        <is>
+          <t>A | 231呎 (开放式)
+$459万
+$19,853/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C21" s="21" t="inlineStr">
+        <is>
+          <t>B | 401呎 (2房)
+$885万
+$22,060/呎
+(23年-02月)</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr">
+        <is>
+          <t>C | 290呎 (1房)
+$673万
+$23,197/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E21" s="21" t="inlineStr">
+        <is>
+          <t>D | 266呎 (开放式)
+$677万
+$25,451/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="F21" s="21" t="inlineStr">
+        <is>
+          <t>E | 266呎 (开放式)
+$648万
+$24,361/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="G21" s="21" t="inlineStr">
+        <is>
+          <t>F | 292呎 (1房)
+$544万
+$18,616/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H21" s="21" t="inlineStr">
+        <is>
+          <t>G | 293呎 (1房)
+$696万
+$23,768/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I21" s="21" t="inlineStr">
+        <is>
+          <t>H | 233呎 (开放式)
+$560万
+$24,039/呎
+(24年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="inlineStr">
+        <is>
+          <t>A | 232呎 (开放式)
+$508万
+$21,914/呎
+(23年-02月)</t>
+        </is>
+      </c>
+      <c r="C22" s="21" t="inlineStr">
+        <is>
+          <t>B | 401呎 (2房)
+$757万
+$18,870/呎
+(22年-11月)</t>
+        </is>
+      </c>
+      <c r="D22" s="21" t="inlineStr">
+        <is>
+          <t>C | 290呎 (1房)
+$666万
+$22,983/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E22" s="21" t="inlineStr">
+        <is>
+          <t>D | 266呎 (开放式)
+$674万
+$25,350/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="F22" s="21" t="inlineStr">
+        <is>
+          <t>E | 266呎 (开放式)
+$508万
+$19,090/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="G22" s="21" t="inlineStr">
+        <is>
+          <t>F | 292呎 (1房)
+$668万
+$22,877/呎
+(23年-03月)</t>
+        </is>
+      </c>
+      <c r="H22" s="21" t="inlineStr">
+        <is>
+          <t>G | 293呎 (1房)
+$700万
+$23,904/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="I22" s="21" t="inlineStr">
+        <is>
+          <t>H | 232呎 (开放式)
+$556万
+$23,948/呎
+(23年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
+        <is>
+          <t>A | 231呎 (开放式)
+$443万
+$19,165/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C23" s="21" t="inlineStr">
+        <is>
+          <t>B | 401呎 (2房)
+$860万
+$21,449/呎
+(23年-02月)</t>
+        </is>
+      </c>
+      <c r="D23" s="21" t="inlineStr">
+        <is>
+          <t>C | 290呎 (1房)
+$656万
+$22,624/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E23" s="21" t="inlineStr">
+        <is>
+          <t>D | 266呎 (开放式)
+$662万
+$24,902/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="F23" s="21" t="inlineStr">
+        <is>
+          <t>E | 266呎 (开放式)
+$630万
+$23,699/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="G23" s="21" t="inlineStr">
+        <is>
+          <t>F | 292呎 (1房)
+$668万
+$22,860/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H23" s="21" t="inlineStr">
+        <is>
+          <t>G | 293呎 (1房)
+$692万
+$23,621/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="I23" s="21" t="inlineStr">
+        <is>
+          <t>H | 233呎 (开放式)
+$603万
+$25,897/呎
+(25年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
+        <is>
+          <t>A | 231呎 (开放式)
+$440万
+$19,035/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="inlineStr">
+        <is>
+          <t>B | 401呎 (2房)
+$722万
+$18,005/呎
+(22年-12月)</t>
+        </is>
+      </c>
+      <c r="D24" s="21" t="inlineStr">
+        <is>
+          <t>C | 290呎 (1房)
+$649万
+$22,372/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E24" s="21" t="inlineStr">
+        <is>
+          <t>D | 266呎 (开放式)
+$656万
+$24,654/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="F24" s="21" t="inlineStr">
+        <is>
+          <t>E | 266呎 (开放式)
+$472万
+$17,741/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="G24" s="21" t="inlineStr">
+        <is>
+          <t>F | 292呎 (1房)
+$670万
+$22,942/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="H24" s="21" t="inlineStr">
+        <is>
+          <t>G | 293呎 (1房)
+$672万
+$22,942/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="I24" s="21" t="inlineStr">
+        <is>
+          <t>H | 232呎 (开放式)
+$537万
+$23,164/呎
+(23年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="inlineStr">
+        <is>
+          <t>A | 232呎 (开放式)
+$416万
+$17,931/呎
+(22年-11月)</t>
+        </is>
+      </c>
+      <c r="C25" s="21" t="inlineStr">
+        <is>
+          <t>B | 401呎 (2房)
+$737万
+$18,389/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D25" s="21" t="inlineStr">
+        <is>
+          <t>C | 290呎 (1房)
+$626万
+$21,583/呎
+(23年-03月)</t>
+        </is>
+      </c>
+      <c r="E25" s="21" t="inlineStr">
+        <is>
+          <t>D | 266呎 (开放式)
+$649万
+$24,414/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F25" s="21" t="inlineStr">
+        <is>
+          <t>E | 266呎 (开放式)
+$659万
+$24,782/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="G25" s="21" t="inlineStr">
+        <is>
+          <t>F | 292呎 (1房)
+$686万
+$23,476/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="H25" s="21" t="inlineStr">
+        <is>
+          <t>G | 293呎 (1房)
+$559万
+$19,092/呎
+(22年-11月)</t>
+        </is>
+      </c>
+      <c r="I25" s="21" t="inlineStr">
+        <is>
+          <t>H | 232呎 (开放式)
+$520万
+$22,422/呎
+(24年-03月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/九龙-长沙湾-连方I.xlsx
+++ b/files/九龙-长沙湾-连方I.xlsx
@@ -116,12 +116,12 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
+      <color rgb="007F7F7F"/>
       <sz val="8"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
+      <color rgb="00660000"/>
       <sz val="8"/>
     </font>
     <font>
@@ -266,13 +266,13 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -653,7 +653,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -8179,11 +8179,40 @@
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="19" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 547呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr"/>
+      <c r="D5" s="21" t="inlineStr"/>
+      <c r="E5" s="21" t="inlineStr"/>
+      <c r="F5" s="21" t="inlineStr"/>
+      <c r="G5" s="20" t="inlineStr">
+        <is>
+          <t>F | 439呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H5" s="21" t="inlineStr"/>
+      <c r="I5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
           <t>27&amp;28</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr"/>
-      <c r="C5" s="21" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t>B | 525呎 (2房)
 $1150万
@@ -8191,7 +8220,7 @@
 (25年-05月)</t>
         </is>
       </c>
-      <c r="D5" s="22" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>C | 411呎 (1房)
 -
@@ -8199,7 +8228,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E5" s="22" t="inlineStr">
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>D | 411呎 (1房)
 -
@@ -8207,7 +8236,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F5" s="22" t="inlineStr">
+      <c r="F6" s="20" t="inlineStr">
         <is>
           <t>E | 525呎 (2房)
 -
@@ -8215,38 +8244,9 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G5" s="20" t="inlineStr"/>
-      <c r="H5" s="20" t="inlineStr"/>
-      <c r="I5" s="20" t="inlineStr"/>
-    </row>
-    <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B6" s="22" t="inlineStr">
-        <is>
-          <t>A | 547呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
-      <c r="E6" s="20" t="inlineStr"/>
-      <c r="F6" s="20" t="inlineStr"/>
-      <c r="G6" s="22" t="inlineStr">
-        <is>
-          <t>F | 439呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="H6" s="20" t="inlineStr"/>
-      <c r="I6" s="20" t="inlineStr"/>
+      <c r="G6" s="21" t="inlineStr"/>
+      <c r="H6" s="21" t="inlineStr"/>
+      <c r="I6" s="21" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
@@ -8254,7 +8254,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>A | 231呎 (开放式)
 $478万
@@ -8262,7 +8262,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>B | 401呎 (2房)
 $1088万
@@ -8270,7 +8270,7 @@
 (24年-04月)</t>
         </is>
       </c>
-      <c r="D7" s="22" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 290呎 (1房)
 -
@@ -8278,7 +8278,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E7" s="22" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>D | 266呎 (开放式)
 -
@@ -8286,7 +8286,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F7" s="22" t="inlineStr">
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>E | 266呎 (开放式)
 -
@@ -8294,7 +8294,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G7" s="22" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>F | 292呎 (1房)
 -
@@ -8302,7 +8302,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H7" s="22" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>G | 293呎 (1房)
 -
@@ -8310,7 +8310,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I7" s="21" t="inlineStr">
+      <c r="I7" s="22" t="inlineStr">
         <is>
           <t>H | 233呎 (开放式)
 $677万
@@ -8325,7 +8325,7 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>A | 231呎 (开放式)
 $473万
@@ -8333,7 +8333,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t>B | 401呎 (2房)
 $1072万
@@ -8349,7 +8349,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E8" s="22" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t>D | 266呎 (开放式)
 -
@@ -8365,7 +8365,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G8" s="21" t="inlineStr">
+      <c r="G8" s="22" t="inlineStr">
         <is>
           <t>F | 292呎 (1房)
 $589万
@@ -8373,7 +8373,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="H8" s="21" t="inlineStr">
+      <c r="H8" s="22" t="inlineStr">
         <is>
           <t>G | 293呎 (1房)
 $660万
@@ -8381,7 +8381,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="I8" s="21" t="inlineStr">
+      <c r="I8" s="22" t="inlineStr">
         <is>
           <t>H | 233呎 (开放式)
 $458万
@@ -8396,7 +8396,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B9" s="21" t="inlineStr">
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>A | 231呎 (开放式)
 $655万
@@ -8404,7 +8404,7 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="C9" s="21" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>B | 401呎 (2房)
 $1056万
@@ -8436,7 +8436,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G9" s="21" t="inlineStr">
+      <c r="G9" s="22" t="inlineStr">
         <is>
           <t>F | 292呎 (1房)
 $577万
@@ -8444,7 +8444,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="H9" s="21" t="inlineStr">
+      <c r="H9" s="22" t="inlineStr">
         <is>
           <t>G | 293呎 (1房)
 $625万
@@ -8452,7 +8452,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="I9" s="21" t="inlineStr">
+      <c r="I9" s="22" t="inlineStr">
         <is>
           <t>H | 233呎 (开放式)
 $594万
@@ -8467,7 +8467,7 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B10" s="21" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>A | 231呎 (开放式)
 $458万
@@ -8475,7 +8475,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="C10" s="21" t="inlineStr">
+      <c r="C10" s="22" t="inlineStr">
         <is>
           <t>B | 401呎 (2房)
 $1040万
@@ -8483,7 +8483,7 @@
 (24年-04月)</t>
         </is>
       </c>
-      <c r="D10" s="21" t="inlineStr">
+      <c r="D10" s="22" t="inlineStr">
         <is>
           <t>C | 290呎 (1房)
 $564万
@@ -8507,7 +8507,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G10" s="21" t="inlineStr">
+      <c r="G10" s="22" t="inlineStr">
         <is>
           <t>F | 292呎 (1房)
 $792万
@@ -8515,7 +8515,7 @@
 (25年-03月)</t>
         </is>
       </c>
-      <c r="H10" s="21" t="inlineStr">
+      <c r="H10" s="22" t="inlineStr">
         <is>
           <t>G | 293呎 (1房)
 $905万
@@ -8523,7 +8523,7 @@
 (25年-05月)</t>
         </is>
       </c>
-      <c r="I10" s="21" t="inlineStr">
+      <c r="I10" s="22" t="inlineStr">
         <is>
           <t>H | 232呎 (开放式)
 $649万
@@ -8538,7 +8538,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B11" s="21" t="inlineStr">
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>A | 231呎 (开放式)
 $454万
@@ -8546,7 +8546,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="C11" s="21" t="inlineStr">
+      <c r="C11" s="22" t="inlineStr">
         <is>
           <t>B | 401呎 (2房)
 $1025万
@@ -8554,7 +8554,7 @@
 (24年-04月)</t>
         </is>
       </c>
-      <c r="D11" s="21" t="inlineStr">
+      <c r="D11" s="22" t="inlineStr">
         <is>
           <t>C | 290呎 (1房)
 $559万
@@ -8578,7 +8578,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G11" s="21" t="inlineStr">
+      <c r="G11" s="22" t="inlineStr">
         <is>
           <t>F | 292呎 (1房)
 $561万
@@ -8586,7 +8586,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="H11" s="21" t="inlineStr">
+      <c r="H11" s="22" t="inlineStr">
         <is>
           <t>G | 293呎 (1房)
 $830万
@@ -8594,7 +8594,7 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="I11" s="21" t="inlineStr">
+      <c r="I11" s="22" t="inlineStr">
         <is>
           <t>H | 233呎 (开放式)
 $642万
@@ -8609,7 +8609,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B12" s="21" t="inlineStr">
+      <c r="B12" s="22" t="inlineStr">
         <is>
           <t>A | 231呎 (开放式)
 $430万
@@ -8617,7 +8617,7 @@
 (25年-07月)</t>
         </is>
       </c>
-      <c r="C12" s="21" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t>B | 401呎 (2房)
 $1010万
@@ -8625,7 +8625,7 @@
 (24年-04月)</t>
         </is>
       </c>
-      <c r="D12" s="21" t="inlineStr">
+      <c r="D12" s="22" t="inlineStr">
         <is>
           <t>C | 290呎 (1房)
 $553万
@@ -8633,7 +8633,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="E12" s="21" t="inlineStr">
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t>D | 266呎 (开放式)
 $602万
@@ -8641,7 +8641,7 @@
 (26年-04月)</t>
         </is>
       </c>
-      <c r="F12" s="21" t="inlineStr">
+      <c r="F12" s="22" t="inlineStr">
         <is>
           <t>E | 266呎 (开放式)
 $517万
@@ -8649,7 +8649,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="G12" s="21" t="inlineStr">
+      <c r="G12" s="22" t="inlineStr">
         <is>
           <t>F | 292呎 (1房)
 $532万
@@ -8657,7 +8657,7 @@
 (25年-08月)</t>
         </is>
       </c>
-      <c r="H12" s="21" t="inlineStr">
+      <c r="H12" s="22" t="inlineStr">
         <is>
           <t>G | 293呎 (1房)
 $822万
@@ -8665,7 +8665,7 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="I12" s="21" t="inlineStr">
+      <c r="I12" s="22" t="inlineStr">
         <is>
           <t>H | 233呎 (开放式)
 $623万
@@ -8680,7 +8680,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B13" s="21" t="inlineStr">
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>A | 232呎 (开放式)
 $613万
@@ -8688,7 +8688,7 @@
 (24年-12月)</t>
         </is>
       </c>
-      <c r="C13" s="21" t="inlineStr">
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t>B | 401呎 (2房)
 $1045万
@@ -8696,7 +8696,7 @@
 (25年-01月)</t>
         </is>
       </c>
-      <c r="D13" s="21" t="inlineStr">
+      <c r="D13" s="22" t="inlineStr">
         <is>
           <t>C | 290呎 (1房)
 $737万
@@ -8704,7 +8704,7 @@
 (24年-04月)</t>
         </is>
       </c>
-      <c r="E13" s="21" t="inlineStr">
+      <c r="E13" s="22" t="inlineStr">
         <is>
           <t>D | 266呎 (开放式)
 $516万
@@ -8712,7 +8712,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="F13" s="21" t="inlineStr">
+      <c r="F13" s="22" t="inlineStr">
         <is>
           <t>E | 266呎 (开放式)
 $514万
@@ -8720,7 +8720,7 @@
 (26年-03月)</t>
         </is>
       </c>
-      <c r="G13" s="21" t="inlineStr">
+      <c r="G13" s="22" t="inlineStr">
         <is>
           <t>F | 292呎 (1房)
 $772万
@@ -8728,7 +8728,7 @@
 (24年-12月)</t>
         </is>
       </c>
-      <c r="H13" s="21" t="inlineStr">
+      <c r="H13" s="22" t="inlineStr">
         <is>
           <t>G | 293呎 (1房)
 $789万
@@ -8736,7 +8736,7 @@
 (24年-06月)</t>
         </is>
       </c>
-      <c r="I13" s="21" t="inlineStr">
+      <c r="I13" s="22" t="inlineStr">
         <is>
           <t>H | 233呎 (开放式)
 $617万
@@ -8751,7 +8751,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B14" s="21" t="inlineStr">
+      <c r="B14" s="22" t="inlineStr">
         <is>
           <t>A | 232呎 (开放式)
 $445万
@@ -8759,7 +8759,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="C14" s="21" t="inlineStr">
+      <c r="C14" s="22" t="inlineStr">
         <is>
           <t>B | 401呎 (2房)
 $995万
@@ -8767,7 +8767,7 @@
 (24年-03月)</t>
         </is>
       </c>
-      <c r="D14" s="21" t="inlineStr">
+      <c r="D14" s="22" t="inlineStr">
         <is>
           <t>C | 290呎 (1房)
 $764万
@@ -8775,7 +8775,7 @@
 (24年-12月)</t>
         </is>
       </c>
-      <c r="E14" s="21" t="inlineStr">
+      <c r="E14" s="22" t="inlineStr">
         <is>
           <t>D | 266呎 (开放式)
 $514万
@@ -8783,7 +8783,7 @@
 (25年-11月)</t>
         </is>
       </c>
-      <c r="F14" s="21" t="inlineStr">
+      <c r="F14" s="22" t="inlineStr">
         <is>
           <t>E | 266呎 (开放式)
 $718万
@@ -8791,7 +8791,7 @@
 (24年-05月)</t>
         </is>
       </c>
-      <c r="G14" s="21" t="inlineStr">
+      <c r="G14" s="22" t="inlineStr">
         <is>
           <t>F | 292呎 (1房)
 $551万
@@ -8799,7 +8799,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="H14" s="21" t="inlineStr">
+      <c r="H14" s="22" t="inlineStr">
         <is>
           <t>G | 293呎 (1房)
 $782万
@@ -8807,7 +8807,7 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="I14" s="21" t="inlineStr">
+      <c r="I14" s="22" t="inlineStr">
         <is>
           <t>H | 232呎 (开放式)
 $617万
@@ -8822,7 +8822,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B15" s="21" t="inlineStr">
+      <c r="B15" s="22" t="inlineStr">
         <is>
           <t>A | 232呎 (开放式)
 $594万
@@ -8830,7 +8830,7 @@
 (24年-05月)</t>
         </is>
       </c>
-      <c r="C15" s="21" t="inlineStr">
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t>B | 401呎 (2房)
 $1034万
@@ -8838,7 +8838,7 @@
 (25年-02月)</t>
         </is>
       </c>
-      <c r="D15" s="21" t="inlineStr">
+      <c r="D15" s="22" t="inlineStr">
         <is>
           <t>C | 290呎 (1房)
 $564万
@@ -8846,7 +8846,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="E15" s="21" t="inlineStr">
+      <c r="E15" s="22" t="inlineStr">
         <is>
           <t>D | 266呎 (开放式)
 $512万
@@ -8854,7 +8854,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="F15" s="21" t="inlineStr">
+      <c r="F15" s="22" t="inlineStr">
         <is>
           <t>E | 266呎 (开放式)
 $704万
@@ -8862,7 +8862,7 @@
 (24年-05月)</t>
         </is>
       </c>
-      <c r="G15" s="21" t="inlineStr">
+      <c r="G15" s="22" t="inlineStr">
         <is>
           <t>F | 292呎 (1房)
 $763万
@@ -8870,7 +8870,7 @@
 (25年-01月)</t>
         </is>
       </c>
-      <c r="H15" s="21" t="inlineStr">
+      <c r="H15" s="22" t="inlineStr">
         <is>
           <t>G | 293呎 (1房)
 $774万
@@ -8878,7 +8878,7 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="I15" s="21" t="inlineStr">
+      <c r="I15" s="22" t="inlineStr">
         <is>
           <t>H | 233呎 (开放式)
 $612万
@@ -8893,7 +8893,7 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B16" s="21" t="inlineStr">
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>A | 232呎 (开放式)
 $588万
@@ -8901,7 +8901,7 @@
 (24年-04月)</t>
         </is>
       </c>
-      <c r="C16" s="21" t="inlineStr">
+      <c r="C16" s="22" t="inlineStr">
         <is>
           <t>B | 401呎 (2房)
 $1040万
@@ -8909,7 +8909,7 @@
 (25年-03月)</t>
         </is>
       </c>
-      <c r="D16" s="21" t="inlineStr">
+      <c r="D16" s="22" t="inlineStr">
         <is>
           <t>C | 290呎 (1房)
 $753万
@@ -8917,7 +8917,7 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="E16" s="21" t="inlineStr">
+      <c r="E16" s="22" t="inlineStr">
         <is>
           <t>D | 266呎 (开放式)
 $712万
@@ -8925,7 +8925,7 @@
 (24年-12月)</t>
         </is>
       </c>
-      <c r="F16" s="21" t="inlineStr">
+      <c r="F16" s="22" t="inlineStr">
         <is>
           <t>E | 266呎 (开放式)
 $687万
@@ -8933,7 +8933,7 @@
 (24年-04月)</t>
         </is>
       </c>
-      <c r="G16" s="21" t="inlineStr">
+      <c r="G16" s="22" t="inlineStr">
         <is>
           <t>F | 292呎 (1房)
 $750万
@@ -8941,7 +8941,7 @@
 (24年-12月)</t>
         </is>
       </c>
-      <c r="H16" s="21" t="inlineStr">
+      <c r="H16" s="22" t="inlineStr">
         <is>
           <t>G | 293呎 (1房)
 $770万
@@ -8949,7 +8949,7 @@
 (24年-09月)</t>
         </is>
       </c>
-      <c r="I16" s="21" t="inlineStr">
+      <c r="I16" s="22" t="inlineStr">
         <is>
           <t>H | 232呎 (开放式)
 $606万
@@ -8964,7 +8964,7 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B17" s="21" t="inlineStr">
+      <c r="B17" s="22" t="inlineStr">
         <is>
           <t>A | 232呎 (开放式)
 $570万
@@ -8972,7 +8972,7 @@
 (24年-04月)</t>
         </is>
       </c>
-      <c r="C17" s="21" t="inlineStr">
+      <c r="C17" s="22" t="inlineStr">
         <is>
           <t>B | 401呎 (2房)
 $1034万
@@ -8980,7 +8980,7 @@
 (25年-03月)</t>
         </is>
       </c>
-      <c r="D17" s="21" t="inlineStr">
+      <c r="D17" s="22" t="inlineStr">
         <is>
           <t>C | 290呎 (1房)
 $748万
@@ -8988,7 +8988,7 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="E17" s="21" t="inlineStr">
+      <c r="E17" s="22" t="inlineStr">
         <is>
           <t>D | 266呎 (开放式)
 $719万
@@ -8996,7 +8996,7 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="F17" s="21" t="inlineStr">
+      <c r="F17" s="22" t="inlineStr">
         <is>
           <t>E | 266呎 (开放式)
 $682万
@@ -9004,7 +9004,7 @@
 (24年-05月)</t>
         </is>
       </c>
-      <c r="G17" s="21" t="inlineStr">
+      <c r="G17" s="22" t="inlineStr">
         <is>
           <t>F | 292呎 (1房)
 $719万
@@ -9012,7 +9012,7 @@
 (24年-05月)</t>
         </is>
       </c>
-      <c r="H17" s="21" t="inlineStr">
+      <c r="H17" s="22" t="inlineStr">
         <is>
           <t>G | 293呎 (1房)
 $766万
@@ -9020,7 +9020,7 @@
 (24年-06月)</t>
         </is>
       </c>
-      <c r="I17" s="21" t="inlineStr">
+      <c r="I17" s="22" t="inlineStr">
         <is>
           <t>H | 233呎 (开放式)
 $588万
@@ -9035,7 +9035,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B18" s="21" t="inlineStr">
+      <c r="B18" s="22" t="inlineStr">
         <is>
           <t>A | 232呎 (开放式)
 $538万
@@ -9043,7 +9043,7 @@
 (23年-04月)</t>
         </is>
       </c>
-      <c r="C18" s="21" t="inlineStr">
+      <c r="C18" s="22" t="inlineStr">
         <is>
           <t>B | 401呎 (2房)
 $805万
@@ -9051,7 +9051,7 @@
 (22年-12月)</t>
         </is>
       </c>
-      <c r="D18" s="21" t="inlineStr">
+      <c r="D18" s="22" t="inlineStr">
         <is>
           <t>C | 290呎 (1房)
 $746万
@@ -9059,7 +9059,7 @@
 (25年-05月)</t>
         </is>
       </c>
-      <c r="E18" s="21" t="inlineStr">
+      <c r="E18" s="22" t="inlineStr">
         <is>
           <t>D | 266呎 (开放式)
 $698万
@@ -9067,7 +9067,7 @@
 (24年-07月)</t>
         </is>
       </c>
-      <c r="F18" s="21" t="inlineStr">
+      <c r="F18" s="22" t="inlineStr">
         <is>
           <t>E | 266呎 (开放式)
 $677万
@@ -9075,7 +9075,7 @@
 (24年-05月)</t>
         </is>
       </c>
-      <c r="G18" s="21" t="inlineStr">
+      <c r="G18" s="22" t="inlineStr">
         <is>
           <t>F | 292呎 (1房)
 $743万
@@ -9083,7 +9083,7 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="H18" s="21" t="inlineStr">
+      <c r="H18" s="22" t="inlineStr">
         <is>
           <t>G | 293呎 (1房)
 $730万
@@ -9091,7 +9091,7 @@
 (24年-04月)</t>
         </is>
       </c>
-      <c r="I18" s="21" t="inlineStr">
+      <c r="I18" s="22" t="inlineStr">
         <is>
           <t>H | 232呎 (开放式)
 $577万
@@ -9114,7 +9114,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C19" s="21" t="inlineStr">
+      <c r="C19" s="22" t="inlineStr">
         <is>
           <t>B | 401呎 (2房)
 $789万
@@ -9122,7 +9122,7 @@
 (22年-12月)</t>
         </is>
       </c>
-      <c r="D19" s="21" t="inlineStr">
+      <c r="D19" s="22" t="inlineStr">
         <is>
           <t>C | 290呎 (1房)
 $732万
@@ -9130,7 +9130,7 @@
 (24年-07月)</t>
         </is>
       </c>
-      <c r="E19" s="21" t="inlineStr">
+      <c r="E19" s="22" t="inlineStr">
         <is>
           <t>D | 266呎 (开放式)
 $691万
@@ -9138,7 +9138,7 @@
 (24年-12月)</t>
         </is>
       </c>
-      <c r="F19" s="21" t="inlineStr">
+      <c r="F19" s="22" t="inlineStr">
         <is>
           <t>E | 266呎 (开放式)
 $673万
@@ -9146,7 +9146,7 @@
 (24年-04月)</t>
         </is>
       </c>
-      <c r="G19" s="21" t="inlineStr">
+      <c r="G19" s="22" t="inlineStr">
         <is>
           <t>F | 292呎 (1房)
 $741万
@@ -9154,7 +9154,7 @@
 (24年-12月)</t>
         </is>
       </c>
-      <c r="H19" s="21" t="inlineStr">
+      <c r="H19" s="22" t="inlineStr">
         <is>
           <t>G | 293呎 (1房)
 $726万
@@ -9162,7 +9162,7 @@
 (24年-04月)</t>
         </is>
       </c>
-      <c r="I19" s="21" t="inlineStr">
+      <c r="I19" s="22" t="inlineStr">
         <is>
           <t>H | 233呎 (开放式)
 $569万
@@ -9177,7 +9177,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B20" s="21" t="inlineStr">
+      <c r="B20" s="22" t="inlineStr">
         <is>
           <t>A | 231呎 (开放式)
 $528万
@@ -9185,7 +9185,7 @@
 (26年-06月)</t>
         </is>
       </c>
-      <c r="C20" s="21" t="inlineStr">
+      <c r="C20" s="22" t="inlineStr">
         <is>
           <t>B | 401呎 (2房)
 $754万
@@ -9193,7 +9193,7 @@
 (22年-11月)</t>
         </is>
       </c>
-      <c r="D20" s="21" t="inlineStr">
+      <c r="D20" s="22" t="inlineStr">
         <is>
           <t>C | 290呎 (1房)
 $684万
@@ -9201,7 +9201,7 @@
 (24年-05月)</t>
         </is>
       </c>
-      <c r="E20" s="21" t="inlineStr">
+      <c r="E20" s="22" t="inlineStr">
         <is>
           <t>D | 266呎 (开放式)
 $684万
@@ -9209,7 +9209,7 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="F20" s="21" t="inlineStr">
+      <c r="F20" s="22" t="inlineStr">
         <is>
           <t>E | 266呎 (开放式)
 $510万
@@ -9217,7 +9217,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="G20" s="21" t="inlineStr">
+      <c r="G20" s="22" t="inlineStr">
         <is>
           <t>F | 292呎 (1房)
 $694万
@@ -9225,7 +9225,7 @@
 (24年-03月)</t>
         </is>
       </c>
-      <c r="H20" s="21" t="inlineStr">
+      <c r="H20" s="22" t="inlineStr">
         <is>
           <t>G | 293呎 (1房)
 $703万
@@ -9233,7 +9233,7 @@
 (24年-04月)</t>
         </is>
       </c>
-      <c r="I20" s="21" t="inlineStr">
+      <c r="I20" s="22" t="inlineStr">
         <is>
           <t>H | 233呎 (开放式)
 $561万
@@ -9248,7 +9248,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B21" s="21" t="inlineStr">
+      <c r="B21" s="22" t="inlineStr">
         <is>
           <t>A | 231呎 (开放式)
 $459万
@@ -9256,7 +9256,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="C21" s="21" t="inlineStr">
+      <c r="C21" s="22" t="inlineStr">
         <is>
           <t>B | 401呎 (2房)
 $885万
@@ -9264,7 +9264,7 @@
 (23年-02月)</t>
         </is>
       </c>
-      <c r="D21" s="21" t="inlineStr">
+      <c r="D21" s="22" t="inlineStr">
         <is>
           <t>C | 290呎 (1房)
 $673万
@@ -9272,7 +9272,7 @@
 (24年-04月)</t>
         </is>
       </c>
-      <c r="E21" s="21" t="inlineStr">
+      <c r="E21" s="22" t="inlineStr">
         <is>
           <t>D | 266呎 (开放式)
 $677万
@@ -9280,7 +9280,7 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="F21" s="21" t="inlineStr">
+      <c r="F21" s="22" t="inlineStr">
         <is>
           <t>E | 266呎 (开放式)
 $648万
@@ -9288,7 +9288,7 @@
 (24年-04月)</t>
         </is>
       </c>
-      <c r="G21" s="21" t="inlineStr">
+      <c r="G21" s="22" t="inlineStr">
         <is>
           <t>F | 292呎 (1房)
 $544万
@@ -9296,7 +9296,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="H21" s="21" t="inlineStr">
+      <c r="H21" s="22" t="inlineStr">
         <is>
           <t>G | 293呎 (1房)
 $696万
@@ -9304,7 +9304,7 @@
 (24年-04月)</t>
         </is>
       </c>
-      <c r="I21" s="21" t="inlineStr">
+      <c r="I21" s="22" t="inlineStr">
         <is>
           <t>H | 233呎 (开放式)
 $560万
@@ -9319,7 +9319,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B22" s="21" t="inlineStr">
+      <c r="B22" s="22" t="inlineStr">
         <is>
           <t>A | 232呎 (开放式)
 $508万
@@ -9327,7 +9327,7 @@
 (23年-02月)</t>
         </is>
       </c>
-      <c r="C22" s="21" t="inlineStr">
+      <c r="C22" s="22" t="inlineStr">
         <is>
           <t>B | 401呎 (2房)
 $757万
@@ -9335,7 +9335,7 @@
 (22年-11月)</t>
         </is>
       </c>
-      <c r="D22" s="21" t="inlineStr">
+      <c r="D22" s="22" t="inlineStr">
         <is>
           <t>C | 290呎 (1房)
 $666万
@@ -9343,7 +9343,7 @@
 (24年-04月)</t>
         </is>
       </c>
-      <c r="E22" s="21" t="inlineStr">
+      <c r="E22" s="22" t="inlineStr">
         <is>
           <t>D | 266呎 (开放式)
 $674万
@@ -9351,7 +9351,7 @@
 (24年-07月)</t>
         </is>
       </c>
-      <c r="F22" s="21" t="inlineStr">
+      <c r="F22" s="22" t="inlineStr">
         <is>
           <t>E | 266呎 (开放式)
 $508万
@@ -9359,7 +9359,7 @@
 (26年-02月)</t>
         </is>
       </c>
-      <c r="G22" s="21" t="inlineStr">
+      <c r="G22" s="22" t="inlineStr">
         <is>
           <t>F | 292呎 (1房)
 $668万
@@ -9367,7 +9367,7 @@
 (23年-03月)</t>
         </is>
       </c>
-      <c r="H22" s="21" t="inlineStr">
+      <c r="H22" s="22" t="inlineStr">
         <is>
           <t>G | 293呎 (1房)
 $700万
@@ -9375,7 +9375,7 @@
 (24年-03月)</t>
         </is>
       </c>
-      <c r="I22" s="21" t="inlineStr">
+      <c r="I22" s="22" t="inlineStr">
         <is>
           <t>H | 232呎 (开放式)
 $556万
@@ -9390,7 +9390,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B23" s="21" t="inlineStr">
+      <c r="B23" s="22" t="inlineStr">
         <is>
           <t>A | 231呎 (开放式)
 $443万
@@ -9398,7 +9398,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="C23" s="21" t="inlineStr">
+      <c r="C23" s="22" t="inlineStr">
         <is>
           <t>B | 401呎 (2房)
 $860万
@@ -9406,7 +9406,7 @@
 (23年-02月)</t>
         </is>
       </c>
-      <c r="D23" s="21" t="inlineStr">
+      <c r="D23" s="22" t="inlineStr">
         <is>
           <t>C | 290呎 (1房)
 $656万
@@ -9414,7 +9414,7 @@
 (24年-04月)</t>
         </is>
       </c>
-      <c r="E23" s="21" t="inlineStr">
+      <c r="E23" s="22" t="inlineStr">
         <is>
           <t>D | 266呎 (开放式)
 $662万
@@ -9422,7 +9422,7 @@
 (24年-12月)</t>
         </is>
       </c>
-      <c r="F23" s="21" t="inlineStr">
+      <c r="F23" s="22" t="inlineStr">
         <is>
           <t>E | 266呎 (开放式)
 $630万
@@ -9430,7 +9430,7 @@
 (24年-03月)</t>
         </is>
       </c>
-      <c r="G23" s="21" t="inlineStr">
+      <c r="G23" s="22" t="inlineStr">
         <is>
           <t>F | 292呎 (1房)
 $668万
@@ -9438,7 +9438,7 @@
 (24年-04月)</t>
         </is>
       </c>
-      <c r="H23" s="21" t="inlineStr">
+      <c r="H23" s="22" t="inlineStr">
         <is>
           <t>G | 293呎 (1房)
 $692万
@@ -9446,7 +9446,7 @@
 (24年-03月)</t>
         </is>
       </c>
-      <c r="I23" s="21" t="inlineStr">
+      <c r="I23" s="22" t="inlineStr">
         <is>
           <t>H | 233呎 (开放式)
 $603万
@@ -9461,7 +9461,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B24" s="21" t="inlineStr">
+      <c r="B24" s="22" t="inlineStr">
         <is>
           <t>A | 231呎 (开放式)
 $440万
@@ -9469,7 +9469,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="C24" s="21" t="inlineStr">
+      <c r="C24" s="22" t="inlineStr">
         <is>
           <t>B | 401呎 (2房)
 $722万
@@ -9477,7 +9477,7 @@
 (22年-12月)</t>
         </is>
       </c>
-      <c r="D24" s="21" t="inlineStr">
+      <c r="D24" s="22" t="inlineStr">
         <is>
           <t>C | 290呎 (1房)
 $649万
@@ -9485,7 +9485,7 @@
 (24年-04月)</t>
         </is>
       </c>
-      <c r="E24" s="21" t="inlineStr">
+      <c r="E24" s="22" t="inlineStr">
         <is>
           <t>D | 266呎 (开放式)
 $656万
@@ -9493,7 +9493,7 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="F24" s="21" t="inlineStr">
+      <c r="F24" s="22" t="inlineStr">
         <is>
           <t>E | 266呎 (开放式)
 $472万
@@ -9501,7 +9501,7 @@
 (25年-11月)</t>
         </is>
       </c>
-      <c r="G24" s="21" t="inlineStr">
+      <c r="G24" s="22" t="inlineStr">
         <is>
           <t>F | 292呎 (1房)
 $670万
@@ -9509,7 +9509,7 @@
 (24年-03月)</t>
         </is>
       </c>
-      <c r="H24" s="21" t="inlineStr">
+      <c r="H24" s="22" t="inlineStr">
         <is>
           <t>G | 293呎 (1房)
 $672万
@@ -9517,7 +9517,7 @@
 (24年-04月)</t>
         </is>
       </c>
-      <c r="I24" s="21" t="inlineStr">
+      <c r="I24" s="22" t="inlineStr">
         <is>
           <t>H | 232呎 (开放式)
 $537万
@@ -9532,7 +9532,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B25" s="21" t="inlineStr">
+      <c r="B25" s="22" t="inlineStr">
         <is>
           <t>A | 232呎 (开放式)
 $416万
@@ -9540,7 +9540,7 @@
 (22年-11月)</t>
         </is>
       </c>
-      <c r="C25" s="21" t="inlineStr">
+      <c r="C25" s="22" t="inlineStr">
         <is>
           <t>B | 401呎 (2房)
 $737万
@@ -9548,7 +9548,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="D25" s="21" t="inlineStr">
+      <c r="D25" s="22" t="inlineStr">
         <is>
           <t>C | 290呎 (1房)
 $626万
@@ -9556,7 +9556,7 @@
 (23年-03月)</t>
         </is>
       </c>
-      <c r="E25" s="21" t="inlineStr">
+      <c r="E25" s="22" t="inlineStr">
         <is>
           <t>D | 266呎 (开放式)
 $649万
@@ -9564,7 +9564,7 @@
 (24年-05月)</t>
         </is>
       </c>
-      <c r="F25" s="21" t="inlineStr">
+      <c r="F25" s="22" t="inlineStr">
         <is>
           <t>E | 266呎 (开放式)
 $659万
@@ -9572,7 +9572,7 @@
 (25年-02月)</t>
         </is>
       </c>
-      <c r="G25" s="21" t="inlineStr">
+      <c r="G25" s="22" t="inlineStr">
         <is>
           <t>F | 292呎 (1房)
 $686万
@@ -9580,7 +9580,7 @@
 (25年-03月)</t>
         </is>
       </c>
-      <c r="H25" s="21" t="inlineStr">
+      <c r="H25" s="22" t="inlineStr">
         <is>
           <t>G | 293呎 (1房)
 $559万
@@ -9588,7 +9588,7 @@
 (22年-11月)</t>
         </is>
       </c>
-      <c r="I25" s="21" t="inlineStr">
+      <c r="I25" s="22" t="inlineStr">
         <is>
           <t>H | 232呎 (开放式)
 $520万

--- a/files/九龙-长沙湾-连方I.xlsx
+++ b/files/九龙-长沙湾-连方I.xlsx
@@ -116,12 +116,12 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
+      <color rgb="00660000"/>
       <sz val="8"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
+      <color rgb="007F7F7F"/>
       <sz val="8"/>
     </font>
     <font>
@@ -266,13 +266,13 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -643,7 +643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J160"/>
+  <dimension ref="A1:N160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -656,6 +656,10 @@
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="23" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -713,6 +717,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -763,6 +787,26 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -813,6 +857,26 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -863,6 +927,26 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -913,6 +997,26 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -959,6 +1063,22 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>11500000</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>21905</v>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1009,6 +1129,26 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1055,6 +1195,22 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>6766000</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>29039</v>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1105,6 +1261,26 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1155,6 +1331,26 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1205,6 +1401,26 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1255,6 +1471,26 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1305,6 +1541,26 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1351,6 +1607,22 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>10881000</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>27135</v>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1397,6 +1669,22 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>4779000</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>20688</v>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1443,6 +1731,22 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>4580000</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>19657</v>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1489,6 +1793,22 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>6603000</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>22536</v>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1535,6 +1855,22 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>5889000</v>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>20168</v>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1581,6 +1917,22 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>5111680</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>19217</v>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>120天即供付款計劃（照售價減5.5%）</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1631,6 +1983,26 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1677,6 +2049,22 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>5439360</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>18756</v>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>120天即供付款計劃（照售價減5.5%）</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1723,6 +2111,22 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>10720000</v>
+      </c>
+      <c r="L23" s="5" t="n">
+        <v>26733</v>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1769,6 +2173,22 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>4732000</v>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>20485</v>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1815,6 +2235,22 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="n">
+        <v>5944000</v>
+      </c>
+      <c r="L25" s="5" t="n">
+        <v>25511</v>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1861,6 +2297,22 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>6253000</v>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>21341</v>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1907,6 +2359,22 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="n">
+        <v>5774000</v>
+      </c>
+      <c r="L27" s="5" t="n">
+        <v>19774</v>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1953,6 +2421,22 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>5011840</v>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>18842</v>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>120天即供付款計劃（照售價減5.5%）</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1999,6 +2483,22 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="n">
+        <v>5011840</v>
+      </c>
+      <c r="L29" s="5" t="n">
+        <v>18842</v>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>120天即供付款計劃（照售價減5.5%）</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2045,6 +2545,22 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>5333120</v>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>18390</v>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>120天即供付款計劃（照售價減5.5%）</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2091,6 +2607,22 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>10561000</v>
+      </c>
+      <c r="L31" s="5" t="n">
+        <v>26337</v>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2137,6 +2669,22 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>6553000</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>28368</v>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2183,6 +2731,22 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v>6486000</v>
+      </c>
+      <c r="L33" s="5" t="n">
+        <v>27957</v>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2229,6 +2793,22 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>9052000</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>30894</v>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2275,6 +2855,22 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="n">
+        <v>7915000</v>
+      </c>
+      <c r="L35" s="5" t="n">
+        <v>27106</v>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2321,6 +2917,22 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>4912640</v>
+      </c>
+      <c r="L36" s="5" t="n">
+        <v>18469</v>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>120天即供付款計劃（照售價減5.5%）</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2367,6 +2979,22 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="n">
+        <v>4913280</v>
+      </c>
+      <c r="L37" s="5" t="n">
+        <v>18471</v>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>120天即供付款計劃（照售價減5.5%）</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2413,6 +3041,22 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>5643000</v>
+      </c>
+      <c r="L38" s="5" t="n">
+        <v>19459</v>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2459,6 +3103,22 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="n">
+        <v>10405000</v>
+      </c>
+      <c r="L39" s="5" t="n">
+        <v>25948</v>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2505,6 +3165,22 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>4585000</v>
+      </c>
+      <c r="L40" s="5" t="n">
+        <v>19848</v>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2551,6 +3227,22 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="n">
+        <v>6425000</v>
+      </c>
+      <c r="L41" s="5" t="n">
+        <v>27575</v>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2597,6 +3289,22 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="n">
+        <v>8298000</v>
+      </c>
+      <c r="L42" s="5" t="n">
+        <v>28321</v>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2643,6 +3351,22 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="n">
+        <v>5609000</v>
+      </c>
+      <c r="L43" s="5" t="n">
+        <v>19209</v>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2689,6 +3413,22 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>4864640</v>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>18288</v>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>120天即供付款計劃（照售價減5.5%）</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2735,6 +3475,22 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="n">
+        <v>4865280</v>
+      </c>
+      <c r="L45" s="5" t="n">
+        <v>18291</v>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>120天即供付款計劃（照售價減5.5%）</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2781,6 +3537,22 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="n">
+        <v>5586000</v>
+      </c>
+      <c r="L46" s="5" t="n">
+        <v>19262</v>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2827,6 +3599,22 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="n">
+        <v>10251000</v>
+      </c>
+      <c r="L47" s="5" t="n">
+        <v>25564</v>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2873,6 +3661,22 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="n">
+        <v>4540000</v>
+      </c>
+      <c r="L48" s="5" t="n">
+        <v>19654</v>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2919,6 +3723,22 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="n">
+        <v>6233000</v>
+      </c>
+      <c r="L49" s="5" t="n">
+        <v>26751</v>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2965,6 +3785,22 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="n">
+        <v>8216000</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>28041</v>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3011,6 +3847,22 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="n">
+        <v>5317000</v>
+      </c>
+      <c r="L51" s="5" t="n">
+        <v>18209</v>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3057,6 +3909,22 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="n">
+        <v>5168000</v>
+      </c>
+      <c r="L52" s="5" t="n">
+        <v>19429</v>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3103,6 +3971,22 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="n">
+        <v>6017000</v>
+      </c>
+      <c r="L53" s="5" t="n">
+        <v>22620</v>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3149,6 +4033,22 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K54" s="5" t="n">
+        <v>5531000</v>
+      </c>
+      <c r="L54" s="5" t="n">
+        <v>19072</v>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3195,6 +4095,22 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="n">
+        <v>10100000</v>
+      </c>
+      <c r="L55" s="5" t="n">
+        <v>25187</v>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3241,6 +4157,22 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K56" s="5" t="n">
+        <v>4300000</v>
+      </c>
+      <c r="L56" s="5" t="n">
+        <v>18615</v>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3287,6 +4219,22 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="n">
+        <v>6173000</v>
+      </c>
+      <c r="L57" s="5" t="n">
+        <v>26494</v>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3333,6 +4281,22 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K58" s="5" t="n">
+        <v>7894000</v>
+      </c>
+      <c r="L58" s="5" t="n">
+        <v>26942</v>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3379,6 +4343,22 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="n">
+        <v>7721000</v>
+      </c>
+      <c r="L59" s="5" t="n">
+        <v>26442</v>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3425,6 +4405,22 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K60" s="5" t="n">
+        <v>5141000</v>
+      </c>
+      <c r="L60" s="5" t="n">
+        <v>19327</v>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3471,6 +4467,22 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="n">
+        <v>5163000</v>
+      </c>
+      <c r="L61" s="5" t="n">
+        <v>19410</v>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3517,6 +4529,22 @@
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K62" s="5" t="n">
+        <v>7371000</v>
+      </c>
+      <c r="L62" s="5" t="n">
+        <v>25417</v>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3563,6 +4591,22 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="n">
+        <v>10447000</v>
+      </c>
+      <c r="L63" s="5" t="n">
+        <v>26052</v>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3609,6 +4653,22 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K64" s="5" t="n">
+        <v>6128000</v>
+      </c>
+      <c r="L64" s="5" t="n">
+        <v>26414</v>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3655,6 +4715,22 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="n">
+        <v>6173000</v>
+      </c>
+      <c r="L65" s="5" t="n">
+        <v>26608</v>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3701,6 +4777,22 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K66" s="5" t="n">
+        <v>7816000</v>
+      </c>
+      <c r="L66" s="5" t="n">
+        <v>26676</v>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3747,6 +4839,22 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="n">
+        <v>5514000</v>
+      </c>
+      <c r="L67" s="5" t="n">
+        <v>18884</v>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3793,6 +4901,22 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K68" s="5" t="n">
+        <v>7183000</v>
+      </c>
+      <c r="L68" s="5" t="n">
+        <v>27004</v>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3839,6 +4963,22 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K69" s="5" t="n">
+        <v>5140000</v>
+      </c>
+      <c r="L69" s="5" t="n">
+        <v>19323</v>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3885,6 +5025,22 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K70" s="5" t="n">
+        <v>7638000</v>
+      </c>
+      <c r="L70" s="5" t="n">
+        <v>26338</v>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N70" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3931,6 +5087,22 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K71" s="5" t="n">
+        <v>9949000</v>
+      </c>
+      <c r="L71" s="5" t="n">
+        <v>24810</v>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N71" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3977,6 +5149,22 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K72" s="5" t="n">
+        <v>4452000</v>
+      </c>
+      <c r="L72" s="5" t="n">
+        <v>19190</v>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N72" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4023,6 +5211,22 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K73" s="5" t="n">
+        <v>6117000</v>
+      </c>
+      <c r="L73" s="5" t="n">
+        <v>26253</v>
+      </c>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N73" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4069,6 +5273,22 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K74" s="5" t="n">
+        <v>7739000</v>
+      </c>
+      <c r="L74" s="5" t="n">
+        <v>26413</v>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N74" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4115,6 +5335,22 @@
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K75" s="5" t="n">
+        <v>7627000</v>
+      </c>
+      <c r="L75" s="5" t="n">
+        <v>26120</v>
+      </c>
+      <c r="M75" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N75" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4161,6 +5397,22 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K76" s="5" t="n">
+        <v>7040000</v>
+      </c>
+      <c r="L76" s="5" t="n">
+        <v>26466</v>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N76" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4207,6 +5459,22 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K77" s="5" t="n">
+        <v>5115000</v>
+      </c>
+      <c r="L77" s="5" t="n">
+        <v>19229</v>
+      </c>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N77" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4253,6 +5521,22 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K78" s="5" t="n">
+        <v>5645000</v>
+      </c>
+      <c r="L78" s="5" t="n">
+        <v>19466</v>
+      </c>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N78" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4299,6 +5583,22 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K79" s="5" t="n">
+        <v>10344000</v>
+      </c>
+      <c r="L79" s="5" t="n">
+        <v>25796</v>
+      </c>
+      <c r="M79" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N79" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4345,6 +5645,22 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K80" s="5" t="n">
+        <v>5945000</v>
+      </c>
+      <c r="L80" s="5" t="n">
+        <v>25625</v>
+      </c>
+      <c r="M80" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N80" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4391,6 +5707,22 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K81" s="5" t="n">
+        <v>6055000</v>
+      </c>
+      <c r="L81" s="5" t="n">
+        <v>26099</v>
+      </c>
+      <c r="M81" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N81" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4437,6 +5769,22 @@
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="5" t="n">
+        <v>7698000</v>
+      </c>
+      <c r="L82" s="5" t="n">
+        <v>26273</v>
+      </c>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N82" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4483,6 +5831,22 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="5" t="n">
+        <v>7503000</v>
+      </c>
+      <c r="L83" s="5" t="n">
+        <v>25695</v>
+      </c>
+      <c r="M83" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N83" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4529,6 +5893,22 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" s="5" t="n">
+        <v>6873000</v>
+      </c>
+      <c r="L84" s="5" t="n">
+        <v>25838</v>
+      </c>
+      <c r="M84" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N84" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4575,6 +5955,22 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="5" t="n">
+        <v>7115000</v>
+      </c>
+      <c r="L85" s="5" t="n">
+        <v>26748</v>
+      </c>
+      <c r="M85" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N85" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4621,6 +6017,22 @@
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K86" s="5" t="n">
+        <v>7529000</v>
+      </c>
+      <c r="L86" s="5" t="n">
+        <v>25962</v>
+      </c>
+      <c r="M86" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N86" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4667,6 +6079,22 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K87" s="5" t="n">
+        <v>10395000</v>
+      </c>
+      <c r="L87" s="5" t="n">
+        <v>25923</v>
+      </c>
+      <c r="M87" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N87" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4713,6 +6141,22 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K88" s="5" t="n">
+        <v>5883000</v>
+      </c>
+      <c r="L88" s="5" t="n">
+        <v>25358</v>
+      </c>
+      <c r="M88" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N88" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4759,6 +6203,22 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K89" s="5" t="n">
+        <v>5877000</v>
+      </c>
+      <c r="L89" s="5" t="n">
+        <v>25223</v>
+      </c>
+      <c r="M89" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N89" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4805,6 +6265,22 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K90" s="5" t="n">
+        <v>7659000</v>
+      </c>
+      <c r="L90" s="5" t="n">
+        <v>26140</v>
+      </c>
+      <c r="M90" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N90" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4851,6 +6327,22 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="5" t="n">
+        <v>7186000</v>
+      </c>
+      <c r="L91" s="5" t="n">
+        <v>24610</v>
+      </c>
+      <c r="M91" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N91" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4897,6 +6389,22 @@
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K92" s="5" t="n">
+        <v>6822000</v>
+      </c>
+      <c r="L92" s="5" t="n">
+        <v>25647</v>
+      </c>
+      <c r="M92" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N92" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4943,6 +6451,22 @@
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K93" s="5" t="n">
+        <v>7191000</v>
+      </c>
+      <c r="L93" s="5" t="n">
+        <v>27034</v>
+      </c>
+      <c r="M93" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N93" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4989,6 +6513,22 @@
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K94" s="5" t="n">
+        <v>7481000</v>
+      </c>
+      <c r="L94" s="5" t="n">
+        <v>25797</v>
+      </c>
+      <c r="M94" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N94" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5035,6 +6575,22 @@
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K95" s="5" t="n">
+        <v>10344000</v>
+      </c>
+      <c r="L95" s="5" t="n">
+        <v>25796</v>
+      </c>
+      <c r="M95" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N95" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5081,6 +6637,22 @@
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K96" s="5" t="n">
+        <v>5700000</v>
+      </c>
+      <c r="L96" s="5" t="n">
+        <v>24569</v>
+      </c>
+      <c r="M96" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N96" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5127,6 +6699,22 @@
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K97" s="5" t="n">
+        <v>5774000</v>
+      </c>
+      <c r="L97" s="5" t="n">
+        <v>24888</v>
+      </c>
+      <c r="M97" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N97" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5173,6 +6761,22 @@
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K98" s="5" t="n">
+        <v>7301000</v>
+      </c>
+      <c r="L98" s="5" t="n">
+        <v>24918</v>
+      </c>
+      <c r="M98" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N98" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5219,6 +6823,22 @@
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" s="5" t="n">
+        <v>7432000</v>
+      </c>
+      <c r="L99" s="5" t="n">
+        <v>25452</v>
+      </c>
+      <c r="M99" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N99" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5265,6 +6885,22 @@
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K100" s="5" t="n">
+        <v>6769000</v>
+      </c>
+      <c r="L100" s="5" t="n">
+        <v>25447</v>
+      </c>
+      <c r="M100" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N100" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5311,6 +6947,22 @@
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K101" s="5" t="n">
+        <v>6975000</v>
+      </c>
+      <c r="L101" s="5" t="n">
+        <v>26222</v>
+      </c>
+      <c r="M101" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N101" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5357,6 +7009,22 @@
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K102" s="5" t="n">
+        <v>7459000</v>
+      </c>
+      <c r="L102" s="5" t="n">
+        <v>25721</v>
+      </c>
+      <c r="M102" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N102" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5403,6 +7071,22 @@
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K103" s="5" t="n">
+        <v>8053000</v>
+      </c>
+      <c r="L103" s="5" t="n">
+        <v>20082</v>
+      </c>
+      <c r="M103" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N103" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5449,6 +7133,22 @@
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K104" s="5" t="n">
+        <v>5377000</v>
+      </c>
+      <c r="L104" s="5" t="n">
+        <v>23177</v>
+      </c>
+      <c r="M104" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N104" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5495,6 +7195,22 @@
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K105" s="5" t="n">
+        <v>5692000</v>
+      </c>
+      <c r="L105" s="5" t="n">
+        <v>24429</v>
+      </c>
+      <c r="M105" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N105" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5541,6 +7257,22 @@
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K106" s="5" t="n">
+        <v>7262000</v>
+      </c>
+      <c r="L106" s="5" t="n">
+        <v>24785</v>
+      </c>
+      <c r="M106" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N106" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5587,6 +7319,22 @@
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K107" s="5" t="n">
+        <v>7407000</v>
+      </c>
+      <c r="L107" s="5" t="n">
+        <v>25366</v>
+      </c>
+      <c r="M107" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N107" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5633,6 +7381,22 @@
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K108" s="5" t="n">
+        <v>6726000</v>
+      </c>
+      <c r="L108" s="5" t="n">
+        <v>25286</v>
+      </c>
+      <c r="M108" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N108" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5679,6 +7443,22 @@
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K109" s="5" t="n">
+        <v>6906000</v>
+      </c>
+      <c r="L109" s="5" t="n">
+        <v>25962</v>
+      </c>
+      <c r="M109" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N109" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5725,6 +7505,22 @@
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K110" s="5" t="n">
+        <v>7316000</v>
+      </c>
+      <c r="L110" s="5" t="n">
+        <v>25228</v>
+      </c>
+      <c r="M110" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N110" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5771,6 +7567,22 @@
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K111" s="5" t="n">
+        <v>7891000</v>
+      </c>
+      <c r="L111" s="5" t="n">
+        <v>19678</v>
+      </c>
+      <c r="M111" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N111" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5817,6 +7629,22 @@
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="K112" s="5" t="n">
+        <v>3477760</v>
+      </c>
+      <c r="L112" s="5" t="n">
+        <v>14990</v>
+      </c>
+      <c r="M112" s="3" t="inlineStr">
+        <is>
+          <t>120天即供付款計劃（照售價減5.5%）</t>
+        </is>
+      </c>
+      <c r="N112" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5863,6 +7691,22 @@
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K113" s="5" t="n">
+        <v>5611000</v>
+      </c>
+      <c r="L113" s="5" t="n">
+        <v>24082</v>
+      </c>
+      <c r="M113" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N113" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5909,6 +7753,22 @@
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K114" s="5" t="n">
+        <v>7030000</v>
+      </c>
+      <c r="L114" s="5" t="n">
+        <v>23993</v>
+      </c>
+      <c r="M114" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N114" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5955,6 +7815,22 @@
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K115" s="5" t="n">
+        <v>6938000</v>
+      </c>
+      <c r="L115" s="5" t="n">
+        <v>23760</v>
+      </c>
+      <c r="M115" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N115" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6001,6 +7877,22 @@
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K116" s="5" t="n">
+        <v>5095000</v>
+      </c>
+      <c r="L116" s="5" t="n">
+        <v>19154</v>
+      </c>
+      <c r="M116" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N116" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6047,6 +7939,22 @@
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K117" s="5" t="n">
+        <v>6837000</v>
+      </c>
+      <c r="L117" s="5" t="n">
+        <v>25703</v>
+      </c>
+      <c r="M117" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N117" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6093,6 +8001,22 @@
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K118" s="5" t="n">
+        <v>6842000</v>
+      </c>
+      <c r="L118" s="5" t="n">
+        <v>23593</v>
+      </c>
+      <c r="M118" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N118" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6139,6 +8063,22 @@
       </c>
       <c r="J119" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K119" s="5" t="n">
+        <v>7535000</v>
+      </c>
+      <c r="L119" s="5" t="n">
+        <v>18791</v>
+      </c>
+      <c r="M119" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N119" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6185,6 +8125,22 @@
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K120" s="5" t="n">
+        <v>5275000</v>
+      </c>
+      <c r="L120" s="5" t="n">
+        <v>22835</v>
+      </c>
+      <c r="M120" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N120" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6231,6 +8187,22 @@
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K121" s="5" t="n">
+        <v>5601000</v>
+      </c>
+      <c r="L121" s="5" t="n">
+        <v>24039</v>
+      </c>
+      <c r="M121" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N121" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6277,6 +8249,22 @@
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K122" s="5" t="n">
+        <v>6964000</v>
+      </c>
+      <c r="L122" s="5" t="n">
+        <v>23768</v>
+      </c>
+      <c r="M122" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N122" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6323,6 +8311,22 @@
       </c>
       <c r="J123" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K123" s="5" t="n">
+        <v>5436000</v>
+      </c>
+      <c r="L123" s="5" t="n">
+        <v>18616</v>
+      </c>
+      <c r="M123" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N123" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6369,6 +8373,22 @@
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K124" s="5" t="n">
+        <v>6480000</v>
+      </c>
+      <c r="L124" s="5" t="n">
+        <v>24361</v>
+      </c>
+      <c r="M124" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N124" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6415,6 +8435,22 @@
       </c>
       <c r="J125" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K125" s="5" t="n">
+        <v>6770000</v>
+      </c>
+      <c r="L125" s="5" t="n">
+        <v>25451</v>
+      </c>
+      <c r="M125" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N125" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6461,6 +8497,22 @@
       </c>
       <c r="J126" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K126" s="5" t="n">
+        <v>6727000</v>
+      </c>
+      <c r="L126" s="5" t="n">
+        <v>23197</v>
+      </c>
+      <c r="M126" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N126" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6507,6 +8559,22 @@
       </c>
       <c r="J127" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K127" s="5" t="n">
+        <v>8846000</v>
+      </c>
+      <c r="L127" s="5" t="n">
+        <v>22060</v>
+      </c>
+      <c r="M127" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N127" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6553,6 +8621,22 @@
       </c>
       <c r="J128" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K128" s="5" t="n">
+        <v>4586000</v>
+      </c>
+      <c r="L128" s="5" t="n">
+        <v>19853</v>
+      </c>
+      <c r="M128" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N128" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6599,6 +8683,22 @@
       </c>
       <c r="J129" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K129" s="5" t="n">
+        <v>5556000</v>
+      </c>
+      <c r="L129" s="5" t="n">
+        <v>23948</v>
+      </c>
+      <c r="M129" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N129" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6645,6 +8745,22 @@
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K130" s="5" t="n">
+        <v>7004000</v>
+      </c>
+      <c r="L130" s="5" t="n">
+        <v>23904</v>
+      </c>
+      <c r="M130" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N130" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6691,6 +8807,22 @@
       </c>
       <c r="J131" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K131" s="5" t="n">
+        <v>6680000</v>
+      </c>
+      <c r="L131" s="5" t="n">
+        <v>22877</v>
+      </c>
+      <c r="M131" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N131" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6737,6 +8869,22 @@
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K132" s="5" t="n">
+        <v>5078000</v>
+      </c>
+      <c r="L132" s="5" t="n">
+        <v>19090</v>
+      </c>
+      <c r="M132" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N132" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6783,6 +8931,22 @@
       </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K133" s="5" t="n">
+        <v>6743000</v>
+      </c>
+      <c r="L133" s="5" t="n">
+        <v>25350</v>
+      </c>
+      <c r="M133" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N133" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6829,6 +8993,22 @@
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K134" s="5" t="n">
+        <v>6665000</v>
+      </c>
+      <c r="L134" s="5" t="n">
+        <v>22983</v>
+      </c>
+      <c r="M134" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N134" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6875,6 +9055,22 @@
       </c>
       <c r="J135" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K135" s="5" t="n">
+        <v>7567000</v>
+      </c>
+      <c r="L135" s="5" t="n">
+        <v>18870</v>
+      </c>
+      <c r="M135" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N135" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6921,6 +9117,22 @@
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K136" s="5" t="n">
+        <v>5084000</v>
+      </c>
+      <c r="L136" s="5" t="n">
+        <v>21914</v>
+      </c>
+      <c r="M136" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N136" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6967,6 +9179,22 @@
       </c>
       <c r="J137" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K137" s="5" t="n">
+        <v>6034000</v>
+      </c>
+      <c r="L137" s="5" t="n">
+        <v>25897</v>
+      </c>
+      <c r="M137" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N137" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7013,6 +9241,22 @@
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K138" s="5" t="n">
+        <v>6921000</v>
+      </c>
+      <c r="L138" s="5" t="n">
+        <v>23621</v>
+      </c>
+      <c r="M138" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N138" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7059,6 +9303,22 @@
       </c>
       <c r="J139" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K139" s="5" t="n">
+        <v>6675000</v>
+      </c>
+      <c r="L139" s="5" t="n">
+        <v>22860</v>
+      </c>
+      <c r="M139" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N139" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7105,6 +9365,22 @@
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K140" s="5" t="n">
+        <v>6304000</v>
+      </c>
+      <c r="L140" s="5" t="n">
+        <v>23699</v>
+      </c>
+      <c r="M140" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N140" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7151,6 +9427,22 @@
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K141" s="5" t="n">
+        <v>6624000</v>
+      </c>
+      <c r="L141" s="5" t="n">
+        <v>24902</v>
+      </c>
+      <c r="M141" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N141" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7197,6 +9489,22 @@
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K142" s="5" t="n">
+        <v>6561000</v>
+      </c>
+      <c r="L142" s="5" t="n">
+        <v>22624</v>
+      </c>
+      <c r="M142" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N142" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7243,6 +9551,22 @@
       </c>
       <c r="J143" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K143" s="5" t="n">
+        <v>8601000</v>
+      </c>
+      <c r="L143" s="5" t="n">
+        <v>21449</v>
+      </c>
+      <c r="M143" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N143" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7289,6 +9613,22 @@
       </c>
       <c r="J144" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K144" s="5" t="n">
+        <v>4427000</v>
+      </c>
+      <c r="L144" s="5" t="n">
+        <v>19165</v>
+      </c>
+      <c r="M144" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N144" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7335,6 +9675,22 @@
       </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K145" s="5" t="n">
+        <v>5374000</v>
+      </c>
+      <c r="L145" s="5" t="n">
+        <v>23164</v>
+      </c>
+      <c r="M145" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N145" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7381,6 +9737,22 @@
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K146" s="5" t="n">
+        <v>6722000</v>
+      </c>
+      <c r="L146" s="5" t="n">
+        <v>22942</v>
+      </c>
+      <c r="M146" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N146" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7427,6 +9799,22 @@
       </c>
       <c r="J147" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K147" s="5" t="n">
+        <v>6699000</v>
+      </c>
+      <c r="L147" s="5" t="n">
+        <v>22942</v>
+      </c>
+      <c r="M147" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N147" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7473,6 +9861,22 @@
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K148" s="5" t="n">
+        <v>4719000</v>
+      </c>
+      <c r="L148" s="5" t="n">
+        <v>17741</v>
+      </c>
+      <c r="M148" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N148" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7519,6 +9923,22 @@
       </c>
       <c r="J149" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K149" s="5" t="n">
+        <v>6558000</v>
+      </c>
+      <c r="L149" s="5" t="n">
+        <v>24654</v>
+      </c>
+      <c r="M149" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N149" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7565,6 +9985,22 @@
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K150" s="5" t="n">
+        <v>6488000</v>
+      </c>
+      <c r="L150" s="5" t="n">
+        <v>22372</v>
+      </c>
+      <c r="M150" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N150" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7611,6 +10047,22 @@
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K151" s="5" t="n">
+        <v>7220000</v>
+      </c>
+      <c r="L151" s="5" t="n">
+        <v>18005</v>
+      </c>
+      <c r="M151" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N151" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7657,6 +10109,22 @@
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K152" s="5" t="n">
+        <v>4397000</v>
+      </c>
+      <c r="L152" s="5" t="n">
+        <v>19035</v>
+      </c>
+      <c r="M152" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N152" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7703,6 +10171,22 @@
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K153" s="5" t="n">
+        <v>5202000</v>
+      </c>
+      <c r="L153" s="5" t="n">
+        <v>22422</v>
+      </c>
+      <c r="M153" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N153" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7749,6 +10233,22 @@
       </c>
       <c r="J154" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K154" s="5" t="n">
+        <v>5594000</v>
+      </c>
+      <c r="L154" s="5" t="n">
+        <v>19092</v>
+      </c>
+      <c r="M154" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N154" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7795,6 +10295,22 @@
       </c>
       <c r="J155" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K155" s="5" t="n">
+        <v>6855000</v>
+      </c>
+      <c r="L155" s="5" t="n">
+        <v>23476</v>
+      </c>
+      <c r="M155" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N155" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7841,6 +10357,22 @@
       </c>
       <c r="J156" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K156" s="5" t="n">
+        <v>6592000</v>
+      </c>
+      <c r="L156" s="5" t="n">
+        <v>24782</v>
+      </c>
+      <c r="M156" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N156" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7887,6 +10419,22 @@
       </c>
       <c r="J157" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K157" s="5" t="n">
+        <v>6494000</v>
+      </c>
+      <c r="L157" s="5" t="n">
+        <v>24414</v>
+      </c>
+      <c r="M157" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N157" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7933,6 +10481,22 @@
       </c>
       <c r="J158" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K158" s="5" t="n">
+        <v>6259000</v>
+      </c>
+      <c r="L158" s="5" t="n">
+        <v>21583</v>
+      </c>
+      <c r="M158" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N158" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7979,6 +10543,22 @@
       </c>
       <c r="J159" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K159" s="5" t="n">
+        <v>7374000</v>
+      </c>
+      <c r="L159" s="5" t="n">
+        <v>18389</v>
+      </c>
+      <c r="M159" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N159" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8025,13 +10605,29 @@
       </c>
       <c r="J160" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K160" s="5" t="n">
+        <v>4160000</v>
+      </c>
+      <c r="L160" s="5" t="n">
+        <v>17931</v>
+      </c>
+      <c r="M160" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N160" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -8179,10 +10775,53 @@
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="19" t="inlineStr">
         <is>
+          <t>27&amp;28</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr"/>
+      <c r="C5" s="21" t="inlineStr">
+        <is>
+          <t>B | 525呎 (2房)
+$1150万
+$21,905/呎
+(25年-05月-07日)</t>
+        </is>
+      </c>
+      <c r="D5" s="22" t="inlineStr">
+        <is>
+          <t>C | 411呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E5" s="22" t="inlineStr">
+        <is>
+          <t>D | 411呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F5" s="22" t="inlineStr">
+        <is>
+          <t>E | 525呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="inlineStr"/>
+      <c r="H5" s="20" t="inlineStr"/>
+      <c r="I5" s="20" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>A | 547呎 (3房)
 -
@@ -8190,11 +10829,11 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C5" s="21" t="inlineStr"/>
-      <c r="D5" s="21" t="inlineStr"/>
-      <c r="E5" s="21" t="inlineStr"/>
-      <c r="F5" s="21" t="inlineStr"/>
-      <c r="G5" s="20" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr"/>
+      <c r="G6" s="22" t="inlineStr">
         <is>
           <t>F | 439呎 (2房)
 -
@@ -8202,51 +10841,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H5" s="21" t="inlineStr"/>
-      <c r="I5" s="21" t="inlineStr"/>
-    </row>
-    <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
-        <is>
-          <t>27&amp;28</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr"/>
-      <c r="C6" s="22" t="inlineStr">
-        <is>
-          <t>B | 525呎 (2房)
-$1150万
-$21,905/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="D6" s="20" t="inlineStr">
-        <is>
-          <t>C | 411呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E6" s="20" t="inlineStr">
-        <is>
-          <t>D | 411呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F6" s="20" t="inlineStr">
-        <is>
-          <t>E | 525呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G6" s="21" t="inlineStr"/>
-      <c r="H6" s="21" t="inlineStr"/>
-      <c r="I6" s="21" t="inlineStr"/>
+      <c r="H6" s="20" t="inlineStr"/>
+      <c r="I6" s="20" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
@@ -8254,23 +10850,23 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B7" s="22" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 231呎 (开放式)
 $478万
 $20,688/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="C7" s="22" t="inlineStr">
+(26年-01月-25日)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 401呎 (2房)
 $1088万
 $27,135/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D7" s="20" t="inlineStr">
+(24年-04月-16日)</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
         <is>
           <t>C | 290呎 (1房)
 -
@@ -8278,7 +10874,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E7" s="20" t="inlineStr">
+      <c r="E7" s="22" t="inlineStr">
         <is>
           <t>D | 266呎 (开放式)
 -
@@ -8286,7 +10882,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F7" s="20" t="inlineStr">
+      <c r="F7" s="22" t="inlineStr">
         <is>
           <t>E | 266呎 (开放式)
 -
@@ -8294,7 +10890,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G7" s="20" t="inlineStr">
+      <c r="G7" s="22" t="inlineStr">
         <is>
           <t>F | 292呎 (1房)
 -
@@ -8302,7 +10898,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H7" s="20" t="inlineStr">
+      <c r="H7" s="22" t="inlineStr">
         <is>
           <t>G | 293呎 (1房)
 -
@@ -8310,12 +10906,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I7" s="22" t="inlineStr">
+      <c r="I7" s="21" t="inlineStr">
         <is>
           <t>H | 233呎 (开放式)
 $677万
 $29,039/呎
-(25年-01月)</t>
+(25年-01月-14日)</t>
         </is>
       </c>
     </row>
@@ -8325,20 +10921,20 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B8" s="22" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>A | 231呎 (开放式)
 $473万
 $20,485/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="C8" s="22" t="inlineStr">
+(26年-01月-22日)</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
         <is>
           <t>B | 401呎 (2房)
 $1072万
 $26,733/呎
-(24年-04月)</t>
+(24年-04月-16日)</t>
         </is>
       </c>
       <c r="D8" s="23" t="inlineStr">
@@ -8349,7 +10945,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E8" s="20" t="inlineStr">
+      <c r="E8" s="22" t="inlineStr">
         <is>
           <t>D | 266呎 (开放式)
 -
@@ -8365,28 +10961,28 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G8" s="22" t="inlineStr">
+      <c r="G8" s="21" t="inlineStr">
         <is>
           <t>F | 292呎 (1房)
 $589万
 $20,168/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="H8" s="22" t="inlineStr">
+(26年-02月-12日)</t>
+        </is>
+      </c>
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t>G | 293呎 (1房)
 $660万
 $22,536/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="I8" s="22" t="inlineStr">
+(26年-02月-11日)</t>
+        </is>
+      </c>
+      <c r="I8" s="21" t="inlineStr">
         <is>
           <t>H | 233呎 (开放式)
 $458万
 $19,657/呎
-(25年-07月)</t>
+(25年-07月-29日)</t>
         </is>
       </c>
     </row>
@@ -8396,20 +10992,20 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B9" s="22" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>A | 231呎 (开放式)
 $655万
 $28,368/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="C9" s="22" t="inlineStr">
+(25年-06月-16日)</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
         <is>
           <t>B | 401呎 (2房)
 $1056万
 $26,337/呎
-(24年-04月)</t>
+(24年-04月-15日)</t>
         </is>
       </c>
       <c r="D9" s="23" t="inlineStr">
@@ -8436,28 +11032,28 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G9" s="22" t="inlineStr">
+      <c r="G9" s="21" t="inlineStr">
         <is>
           <t>F | 292呎 (1房)
 $577万
 $19,774/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="H9" s="22" t="inlineStr">
+(26年-02月-12日)</t>
+        </is>
+      </c>
+      <c r="H9" s="21" t="inlineStr">
         <is>
           <t>G | 293呎 (1房)
 $625万
 $21,341/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="I9" s="22" t="inlineStr">
+(25年-07月-28日)</t>
+        </is>
+      </c>
+      <c r="I9" s="21" t="inlineStr">
         <is>
           <t>H | 233呎 (开放式)
 $594万
 $25,511/呎
-(25年-06月)</t>
+(25年-06月-16日)</t>
         </is>
       </c>
     </row>
@@ -8467,28 +11063,28 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B10" s="22" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>A | 231呎 (开放式)
 $458万
 $19,848/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="C10" s="22" t="inlineStr">
+(26年-01月-06日)</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t>B | 401呎 (2房)
 $1040万
 $25,948/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D10" s="22" t="inlineStr">
+(24年-04月-10日)</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t>C | 290呎 (1房)
 $564万
 $19,459/呎
-(26年-01月)</t>
+(26年-01月-26日)</t>
         </is>
       </c>
       <c r="E10" s="23" t="inlineStr">
@@ -8507,28 +11103,28 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G10" s="22" t="inlineStr">
+      <c r="G10" s="21" t="inlineStr">
         <is>
           <t>F | 292呎 (1房)
 $792万
 $27,106/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="H10" s="22" t="inlineStr">
+(25年-03月-09日)</t>
+        </is>
+      </c>
+      <c r="H10" s="21" t="inlineStr">
         <is>
           <t>G | 293呎 (1房)
 $905万
 $30,894/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="I10" s="22" t="inlineStr">
+(25年-05月-12日)</t>
+        </is>
+      </c>
+      <c r="I10" s="21" t="inlineStr">
         <is>
           <t>H | 232呎 (开放式)
 $649万
 $27,957/呎
-(24年-12月)</t>
+(24年-12月-23日)</t>
         </is>
       </c>
     </row>
@@ -8538,28 +11134,28 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B11" s="22" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>A | 231呎 (开放式)
 $454万
 $19,654/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="C11" s="22" t="inlineStr">
+(26年-01月-12日)</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
         <is>
           <t>B | 401呎 (2房)
 $1025万
 $25,564/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D11" s="22" t="inlineStr">
+(24年-04月-08日)</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t>C | 290呎 (1房)
 $559万
 $19,262/呎
-(26年-01月)</t>
+(26年-01月-19日)</t>
         </is>
       </c>
       <c r="E11" s="23" t="inlineStr">
@@ -8578,28 +11174,28 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G11" s="22" t="inlineStr">
+      <c r="G11" s="21" t="inlineStr">
         <is>
           <t>F | 292呎 (1房)
 $561万
 $19,209/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="H11" s="22" t="inlineStr">
+(26年-01月-22日)</t>
+        </is>
+      </c>
+      <c r="H11" s="21" t="inlineStr">
         <is>
           <t>G | 293呎 (1房)
 $830万
 $28,321/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="I11" s="22" t="inlineStr">
+(24年-11月-26日)</t>
+        </is>
+      </c>
+      <c r="I11" s="21" t="inlineStr">
         <is>
           <t>H | 233呎 (开放式)
 $642万
 $27,575/呎
-(24年-12月)</t>
+(24年-12月-23日)</t>
         </is>
       </c>
     </row>
@@ -8609,68 +11205,68 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B12" s="22" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>A | 231呎 (开放式)
 $430万
 $18,615/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C12" s="22" t="inlineStr">
+(25年-07月-29日)</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
         <is>
           <t>B | 401呎 (2房)
 $1010万
 $25,187/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D12" s="22" t="inlineStr">
+(24年-04月-01日)</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t>C | 290呎 (1房)
 $553万
 $19,072/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="E12" s="22" t="inlineStr">
+(25年-12月-15日)</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
         <is>
           <t>D | 266呎 (开放式)
 $602万
 $22,620/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="F12" s="22" t="inlineStr">
+(26年-04月-19日)</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr">
         <is>
           <t>E | 266呎 (开放式)
 $517万
 $19,429/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="G12" s="22" t="inlineStr">
+(26年-02月-04日)</t>
+        </is>
+      </c>
+      <c r="G12" s="21" t="inlineStr">
         <is>
           <t>F | 292呎 (1房)
 $532万
 $18,209/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="H12" s="22" t="inlineStr">
+(25年-08月-18日)</t>
+        </is>
+      </c>
+      <c r="H12" s="21" t="inlineStr">
         <is>
           <t>G | 293呎 (1房)
 $822万
 $28,041/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="I12" s="22" t="inlineStr">
+(24年-11月-18日)</t>
+        </is>
+      </c>
+      <c r="I12" s="21" t="inlineStr">
         <is>
           <t>H | 233呎 (开放式)
 $623万
 $26,751/呎
-(24年-04月)</t>
+(24年-04月-25日)</t>
         </is>
       </c>
     </row>
@@ -8680,68 +11276,68 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B13" s="22" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t>A | 232呎 (开放式)
 $613万
 $26,414/呎
-(24年-12月)</t>
-        </is>
-      </c>
-      <c r="C13" s="22" t="inlineStr">
+(24年-12月-11日)</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
         <is>
           <t>B | 401呎 (2房)
 $1045万
 $26,052/呎
-(25年-01月)</t>
-        </is>
-      </c>
-      <c r="D13" s="22" t="inlineStr">
+(25年-01月-02日)</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t>C | 290呎 (1房)
 $737万
 $25,417/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E13" s="22" t="inlineStr">
+(24年-04月-22日)</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="inlineStr">
         <is>
           <t>D | 266呎 (开放式)
 $516万
 $19,410/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="F13" s="22" t="inlineStr">
+(26年-01月-15日)</t>
+        </is>
+      </c>
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t>E | 266呎 (开放式)
 $514万
 $19,327/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="G13" s="22" t="inlineStr">
+(26年-03月-02日)</t>
+        </is>
+      </c>
+      <c r="G13" s="21" t="inlineStr">
         <is>
           <t>F | 292呎 (1房)
 $772万
 $26,442/呎
-(24年-12月)</t>
-        </is>
-      </c>
-      <c r="H13" s="22" t="inlineStr">
+(24年-12月-11日)</t>
+        </is>
+      </c>
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t>G | 293呎 (1房)
 $789万
 $26,942/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="I13" s="22" t="inlineStr">
+(24年-06月-02日)</t>
+        </is>
+      </c>
+      <c r="I13" s="21" t="inlineStr">
         <is>
           <t>H | 233呎 (开放式)
 $617万
 $26,494/呎
-(24年-05月)</t>
+(24年-05月-09日)</t>
         </is>
       </c>
     </row>
@@ -8751,68 +11347,68 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B14" s="22" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>A | 232呎 (开放式)
 $445万
 $19,190/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="C14" s="22" t="inlineStr">
+(25年-12月-16日)</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
         <is>
           <t>B | 401呎 (2房)
 $995万
 $24,810/呎
-(24年-03月)</t>
-        </is>
-      </c>
-      <c r="D14" s="22" t="inlineStr">
+(24年-03月-26日)</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t>C | 290呎 (1房)
 $764万
 $26,338/呎
-(24年-12月)</t>
-        </is>
-      </c>
-      <c r="E14" s="22" t="inlineStr">
+(24年-12月-05日)</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="inlineStr">
         <is>
           <t>D | 266呎 (开放式)
 $514万
 $19,323/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="F14" s="22" t="inlineStr">
+(25年-11月-26日)</t>
+        </is>
+      </c>
+      <c r="F14" s="21" t="inlineStr">
         <is>
           <t>E | 266呎 (开放式)
 $718万
 $27,004/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G14" s="22" t="inlineStr">
+(24年-05月-08日)</t>
+        </is>
+      </c>
+      <c r="G14" s="21" t="inlineStr">
         <is>
           <t>F | 292呎 (1房)
 $551万
 $18,884/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="H14" s="22" t="inlineStr">
+(26年-02月-01日)</t>
+        </is>
+      </c>
+      <c r="H14" s="21" t="inlineStr">
         <is>
           <t>G | 293呎 (1房)
 $782万
 $26,676/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="I14" s="22" t="inlineStr">
+(24年-11月-12日)</t>
+        </is>
+      </c>
+      <c r="I14" s="21" t="inlineStr">
         <is>
           <t>H | 232呎 (开放式)
 $617万
 $26,608/呎
-(24年-05月)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
     </row>
@@ -8822,68 +11418,68 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B15" s="22" t="inlineStr">
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t>A | 232呎 (开放式)
 $594万
 $25,625/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C15" s="22" t="inlineStr">
+(24年-05月-13日)</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="inlineStr">
         <is>
           <t>B | 401呎 (2房)
 $1034万
 $25,796/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="D15" s="22" t="inlineStr">
+(25年-02月-06日)</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
         <is>
           <t>C | 290呎 (1房)
 $564万
 $19,466/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="E15" s="22" t="inlineStr">
+(26年-02月-15日)</t>
+        </is>
+      </c>
+      <c r="E15" s="21" t="inlineStr">
         <is>
           <t>D | 266呎 (开放式)
 $512万
 $19,229/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="F15" s="22" t="inlineStr">
+(26年-02月-08日)</t>
+        </is>
+      </c>
+      <c r="F15" s="21" t="inlineStr">
         <is>
           <t>E | 266呎 (开放式)
 $704万
 $26,466/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G15" s="22" t="inlineStr">
+(24年-05月-20日)</t>
+        </is>
+      </c>
+      <c r="G15" s="21" t="inlineStr">
         <is>
           <t>F | 292呎 (1房)
 $763万
 $26,120/呎
-(25年-01月)</t>
-        </is>
-      </c>
-      <c r="H15" s="22" t="inlineStr">
+(25年-01月-05日)</t>
+        </is>
+      </c>
+      <c r="H15" s="21" t="inlineStr">
         <is>
           <t>G | 293呎 (1房)
 $774万
 $26,413/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="I15" s="22" t="inlineStr">
+(24年-11月-19日)</t>
+        </is>
+      </c>
+      <c r="I15" s="21" t="inlineStr">
         <is>
           <t>H | 233呎 (开放式)
 $612万
 $26,253/呎
-(24年-05月)</t>
+(24年-05月-13日)</t>
         </is>
       </c>
     </row>
@@ -8893,68 +11489,68 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B16" s="22" t="inlineStr">
+      <c r="B16" s="21" t="inlineStr">
         <is>
           <t>A | 232呎 (开放式)
 $588万
 $25,358/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C16" s="22" t="inlineStr">
+(24年-04月-16日)</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
         <is>
           <t>B | 401呎 (2房)
 $1040万
 $25,923/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="D16" s="22" t="inlineStr">
+(25年-03月-06日)</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="inlineStr">
         <is>
           <t>C | 290呎 (1房)
 $753万
 $25,962/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="E16" s="22" t="inlineStr">
+(24年-11月-21日)</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="inlineStr">
         <is>
           <t>D | 266呎 (开放式)
 $712万
 $26,748/呎
-(24年-12月)</t>
-        </is>
-      </c>
-      <c r="F16" s="22" t="inlineStr">
+(24年-12月-17日)</t>
+        </is>
+      </c>
+      <c r="F16" s="21" t="inlineStr">
         <is>
           <t>E | 266呎 (开放式)
 $687万
 $25,838/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G16" s="22" t="inlineStr">
+(24年-04月-25日)</t>
+        </is>
+      </c>
+      <c r="G16" s="21" t="inlineStr">
         <is>
           <t>F | 292呎 (1房)
 $750万
 $25,695/呎
-(24年-12月)</t>
-        </is>
-      </c>
-      <c r="H16" s="22" t="inlineStr">
+(24年-12月-17日)</t>
+        </is>
+      </c>
+      <c r="H16" s="21" t="inlineStr">
         <is>
           <t>G | 293呎 (1房)
 $770万
 $26,273/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="I16" s="22" t="inlineStr">
+(24年-09月-24日)</t>
+        </is>
+      </c>
+      <c r="I16" s="21" t="inlineStr">
         <is>
           <t>H | 232呎 (开放式)
 $606万
 $26,099/呎
-(24年-04月)</t>
+(24年-04月-24日)</t>
         </is>
       </c>
     </row>
@@ -8964,68 +11560,68 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B17" s="22" t="inlineStr">
+      <c r="B17" s="21" t="inlineStr">
         <is>
           <t>A | 232呎 (开放式)
 $570万
 $24,569/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C17" s="22" t="inlineStr">
+(24年-04月-17日)</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="inlineStr">
         <is>
           <t>B | 401呎 (2房)
 $1034万
 $25,796/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="D17" s="22" t="inlineStr">
+(25年-03月-27日)</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="inlineStr">
         <is>
           <t>C | 290呎 (1房)
 $748万
 $25,797/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="E17" s="22" t="inlineStr">
+(24年-11月-21日)</t>
+        </is>
+      </c>
+      <c r="E17" s="21" t="inlineStr">
         <is>
           <t>D | 266呎 (开放式)
 $719万
 $27,034/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="F17" s="22" t="inlineStr">
+(24年-11月-21日)</t>
+        </is>
+      </c>
+      <c r="F17" s="21" t="inlineStr">
         <is>
           <t>E | 266呎 (开放式)
 $682万
 $25,647/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G17" s="22" t="inlineStr">
+(24年-05月-19日)</t>
+        </is>
+      </c>
+      <c r="G17" s="21" t="inlineStr">
         <is>
           <t>F | 292呎 (1房)
 $719万
 $24,610/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="H17" s="22" t="inlineStr">
+(24年-05月-08日)</t>
+        </is>
+      </c>
+      <c r="H17" s="21" t="inlineStr">
         <is>
           <t>G | 293呎 (1房)
 $766万
 $26,140/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="I17" s="22" t="inlineStr">
+(24年-06月-10日)</t>
+        </is>
+      </c>
+      <c r="I17" s="21" t="inlineStr">
         <is>
           <t>H | 233呎 (开放式)
 $588万
 $25,223/呎
-(24年-04月)</t>
+(24年-04月-02日)</t>
         </is>
       </c>
     </row>
@@ -9035,68 +11631,68 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B18" s="22" t="inlineStr">
+      <c r="B18" s="21" t="inlineStr">
         <is>
           <t>A | 232呎 (开放式)
 $538万
 $23,177/呎
-(23年-04月)</t>
-        </is>
-      </c>
-      <c r="C18" s="22" t="inlineStr">
+(23年-04月-05日)</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="inlineStr">
         <is>
           <t>B | 401呎 (2房)
 $805万
 $20,082/呎
-(22年-12月)</t>
-        </is>
-      </c>
-      <c r="D18" s="22" t="inlineStr">
+(22年-12月-01日)</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="inlineStr">
         <is>
           <t>C | 290呎 (1房)
 $746万
 $25,721/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="E18" s="22" t="inlineStr">
+(25年-05月-21日)</t>
+        </is>
+      </c>
+      <c r="E18" s="21" t="inlineStr">
         <is>
           <t>D | 266呎 (开放式)
 $698万
 $26,222/呎
-(24年-07月)</t>
-        </is>
-      </c>
-      <c r="F18" s="22" t="inlineStr">
+(24年-07月-01日)</t>
+        </is>
+      </c>
+      <c r="F18" s="21" t="inlineStr">
         <is>
           <t>E | 266呎 (开放式)
 $677万
 $25,447/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G18" s="22" t="inlineStr">
+(24年-05月-13日)</t>
+        </is>
+      </c>
+      <c r="G18" s="21" t="inlineStr">
         <is>
           <t>F | 292呎 (1房)
 $743万
 $25,452/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="H18" s="22" t="inlineStr">
+(24年-11月-21日)</t>
+        </is>
+      </c>
+      <c r="H18" s="21" t="inlineStr">
         <is>
           <t>G | 293呎 (1房)
 $730万
 $24,918/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="I18" s="22" t="inlineStr">
+(24年-04月-17日)</t>
+        </is>
+      </c>
+      <c r="I18" s="21" t="inlineStr">
         <is>
           <t>H | 232呎 (开放式)
 $577万
 $24,888/呎
-(24年-04月)</t>
+(24年-04月-17日)</t>
         </is>
       </c>
     </row>
@@ -9114,60 +11710,60 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C19" s="22" t="inlineStr">
+      <c r="C19" s="21" t="inlineStr">
         <is>
           <t>B | 401呎 (2房)
 $789万
 $19,678/呎
-(22年-12月)</t>
-        </is>
-      </c>
-      <c r="D19" s="22" t="inlineStr">
+(22年-12月-12日)</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="inlineStr">
         <is>
           <t>C | 290呎 (1房)
 $732万
 $25,228/呎
-(24年-07月)</t>
-        </is>
-      </c>
-      <c r="E19" s="22" t="inlineStr">
+(24年-07月-01日)</t>
+        </is>
+      </c>
+      <c r="E19" s="21" t="inlineStr">
         <is>
           <t>D | 266呎 (开放式)
 $691万
 $25,962/呎
-(24年-12月)</t>
-        </is>
-      </c>
-      <c r="F19" s="22" t="inlineStr">
+(24年-12月-23日)</t>
+        </is>
+      </c>
+      <c r="F19" s="21" t="inlineStr">
         <is>
           <t>E | 266呎 (开放式)
 $673万
 $25,286/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G19" s="22" t="inlineStr">
+(24年-04月-17日)</t>
+        </is>
+      </c>
+      <c r="G19" s="21" t="inlineStr">
         <is>
           <t>F | 292呎 (1房)
 $741万
 $25,366/呎
-(24年-12月)</t>
-        </is>
-      </c>
-      <c r="H19" s="22" t="inlineStr">
+(24年-12月-03日)</t>
+        </is>
+      </c>
+      <c r="H19" s="21" t="inlineStr">
         <is>
           <t>G | 293呎 (1房)
 $726万
 $24,785/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="I19" s="22" t="inlineStr">
+(24年-04月-25日)</t>
+        </is>
+      </c>
+      <c r="I19" s="21" t="inlineStr">
         <is>
           <t>H | 233呎 (开放式)
 $569万
 $24,429/呎
-(24年-04月)</t>
+(24年-04月-17日)</t>
         </is>
       </c>
     </row>
@@ -9177,68 +11773,68 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B20" s="22" t="inlineStr">
+      <c r="B20" s="21" t="inlineStr">
         <is>
           <t>A | 231呎 (开放式)
 $528万
 $22,835/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C20" s="22" t="inlineStr">
+(26年-06月-04日)</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="inlineStr">
         <is>
           <t>B | 401呎 (2房)
 $754万
 $18,791/呎
-(22年-11月)</t>
-        </is>
-      </c>
-      <c r="D20" s="22" t="inlineStr">
+(22年-11月-29日)</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="inlineStr">
         <is>
           <t>C | 290呎 (1房)
 $684万
 $23,593/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E20" s="22" t="inlineStr">
+(24年-05月-01日)</t>
+        </is>
+      </c>
+      <c r="E20" s="21" t="inlineStr">
         <is>
           <t>D | 266呎 (开放式)
 $684万
 $25,703/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="F20" s="22" t="inlineStr">
+(24年-11月-21日)</t>
+        </is>
+      </c>
+      <c r="F20" s="21" t="inlineStr">
         <is>
           <t>E | 266呎 (开放式)
 $510万
 $19,154/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="G20" s="22" t="inlineStr">
+(26年-02月-15日)</t>
+        </is>
+      </c>
+      <c r="G20" s="21" t="inlineStr">
         <is>
           <t>F | 292呎 (1房)
 $694万
 $23,760/呎
-(24年-03月)</t>
-        </is>
-      </c>
-      <c r="H20" s="22" t="inlineStr">
+(24年-03月-25日)</t>
+        </is>
+      </c>
+      <c r="H20" s="21" t="inlineStr">
         <is>
           <t>G | 293呎 (1房)
 $703万
 $23,993/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="I20" s="22" t="inlineStr">
+(24年-04月-14日)</t>
+        </is>
+      </c>
+      <c r="I20" s="21" t="inlineStr">
         <is>
           <t>H | 233呎 (开放式)
 $561万
 $24,082/呎
-(24年-04月)</t>
+(24年-04月-17日)</t>
         </is>
       </c>
     </row>
@@ -9248,68 +11844,68 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B21" s="22" t="inlineStr">
+      <c r="B21" s="21" t="inlineStr">
         <is>
           <t>A | 231呎 (开放式)
 $459万
 $19,853/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="C21" s="22" t="inlineStr">
+(26年-02月-05日)</t>
+        </is>
+      </c>
+      <c r="C21" s="21" t="inlineStr">
         <is>
           <t>B | 401呎 (2房)
 $885万
 $22,060/呎
-(23年-02月)</t>
-        </is>
-      </c>
-      <c r="D21" s="22" t="inlineStr">
+(23年-02月-21日)</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr">
         <is>
           <t>C | 290呎 (1房)
 $673万
 $23,197/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E21" s="22" t="inlineStr">
+(24年-04月-17日)</t>
+        </is>
+      </c>
+      <c r="E21" s="21" t="inlineStr">
         <is>
           <t>D | 266呎 (开放式)
 $677万
 $25,451/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="F21" s="22" t="inlineStr">
+(24年-11月-18日)</t>
+        </is>
+      </c>
+      <c r="F21" s="21" t="inlineStr">
         <is>
           <t>E | 266呎 (开放式)
 $648万
 $24,361/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G21" s="22" t="inlineStr">
+(24年-04月-17日)</t>
+        </is>
+      </c>
+      <c r="G21" s="21" t="inlineStr">
         <is>
           <t>F | 292呎 (1房)
 $544万
 $18,616/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="H21" s="22" t="inlineStr">
+(26年-02月-12日)</t>
+        </is>
+      </c>
+      <c r="H21" s="21" t="inlineStr">
         <is>
           <t>G | 293呎 (1房)
 $696万
 $23,768/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="I21" s="22" t="inlineStr">
+(24年-04月-02日)</t>
+        </is>
+      </c>
+      <c r="I21" s="21" t="inlineStr">
         <is>
           <t>H | 233呎 (开放式)
 $560万
 $24,039/呎
-(24年-03月)</t>
+(24年-03月-26日)</t>
         </is>
       </c>
     </row>
@@ -9319,68 +11915,68 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B22" s="22" t="inlineStr">
+      <c r="B22" s="21" t="inlineStr">
         <is>
           <t>A | 232呎 (开放式)
 $508万
 $21,914/呎
-(23年-02月)</t>
-        </is>
-      </c>
-      <c r="C22" s="22" t="inlineStr">
+(23年-02月-13日)</t>
+        </is>
+      </c>
+      <c r="C22" s="21" t="inlineStr">
         <is>
           <t>B | 401呎 (2房)
 $757万
 $18,870/呎
-(22年-11月)</t>
-        </is>
-      </c>
-      <c r="D22" s="22" t="inlineStr">
+(22年-11月-29日)</t>
+        </is>
+      </c>
+      <c r="D22" s="21" t="inlineStr">
         <is>
           <t>C | 290呎 (1房)
 $666万
 $22,983/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E22" s="22" t="inlineStr">
+(24年-04月-17日)</t>
+        </is>
+      </c>
+      <c r="E22" s="21" t="inlineStr">
         <is>
           <t>D | 266呎 (开放式)
 $674万
 $25,350/呎
-(24年-07月)</t>
-        </is>
-      </c>
-      <c r="F22" s="22" t="inlineStr">
+(24年-07月-21日)</t>
+        </is>
+      </c>
+      <c r="F22" s="21" t="inlineStr">
         <is>
           <t>E | 266呎 (开放式)
 $508万
 $19,090/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="G22" s="22" t="inlineStr">
+(26年-02月-24日)</t>
+        </is>
+      </c>
+      <c r="G22" s="21" t="inlineStr">
         <is>
           <t>F | 292呎 (1房)
 $668万
 $22,877/呎
-(23年-03月)</t>
-        </is>
-      </c>
-      <c r="H22" s="22" t="inlineStr">
+(23年-03月-27日)</t>
+        </is>
+      </c>
+      <c r="H22" s="21" t="inlineStr">
         <is>
           <t>G | 293呎 (1房)
 $700万
 $23,904/呎
-(24年-03月)</t>
-        </is>
-      </c>
-      <c r="I22" s="22" t="inlineStr">
+(24年-03月-09日)</t>
+        </is>
+      </c>
+      <c r="I22" s="21" t="inlineStr">
         <is>
           <t>H | 232呎 (开放式)
 $556万
 $23,948/呎
-(23年-07月)</t>
+(23年-07月-13日)</t>
         </is>
       </c>
     </row>
@@ -9390,68 +11986,68 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B23" s="22" t="inlineStr">
+      <c r="B23" s="21" t="inlineStr">
         <is>
           <t>A | 231呎 (开放式)
 $443万
 $19,165/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="C23" s="22" t="inlineStr">
+(26年-01月-26日)</t>
+        </is>
+      </c>
+      <c r="C23" s="21" t="inlineStr">
         <is>
           <t>B | 401呎 (2房)
 $860万
 $21,449/呎
-(23年-02月)</t>
-        </is>
-      </c>
-      <c r="D23" s="22" t="inlineStr">
+(23年-02月-23日)</t>
+        </is>
+      </c>
+      <c r="D23" s="21" t="inlineStr">
         <is>
           <t>C | 290呎 (1房)
 $656万
 $22,624/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E23" s="22" t="inlineStr">
+(24年-04月-09日)</t>
+        </is>
+      </c>
+      <c r="E23" s="21" t="inlineStr">
         <is>
           <t>D | 266呎 (开放式)
 $662万
 $24,902/呎
-(24年-12月)</t>
-        </is>
-      </c>
-      <c r="F23" s="22" t="inlineStr">
+(24年-12月-11日)</t>
+        </is>
+      </c>
+      <c r="F23" s="21" t="inlineStr">
         <is>
           <t>E | 266呎 (开放式)
 $630万
 $23,699/呎
-(24年-03月)</t>
-        </is>
-      </c>
-      <c r="G23" s="22" t="inlineStr">
+(24年-03月-26日)</t>
+        </is>
+      </c>
+      <c r="G23" s="21" t="inlineStr">
         <is>
           <t>F | 292呎 (1房)
 $668万
 $22,860/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="H23" s="22" t="inlineStr">
+(24年-04月-22日)</t>
+        </is>
+      </c>
+      <c r="H23" s="21" t="inlineStr">
         <is>
           <t>G | 293呎 (1房)
 $692万
 $23,621/呎
-(24年-03月)</t>
-        </is>
-      </c>
-      <c r="I23" s="22" t="inlineStr">
+(24年-03月-20日)</t>
+        </is>
+      </c>
+      <c r="I23" s="21" t="inlineStr">
         <is>
           <t>H | 233呎 (开放式)
 $603万
 $25,897/呎
-(25年-06月)</t>
+(25年-06月-16日)</t>
         </is>
       </c>
     </row>
@@ -9461,68 +12057,68 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B24" s="22" t="inlineStr">
+      <c r="B24" s="21" t="inlineStr">
         <is>
           <t>A | 231呎 (开放式)
 $440万
 $19,035/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="C24" s="22" t="inlineStr">
+(26年-01月-22日)</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="inlineStr">
         <is>
           <t>B | 401呎 (2房)
 $722万
 $18,005/呎
-(22年-12月)</t>
-        </is>
-      </c>
-      <c r="D24" s="22" t="inlineStr">
+(22年-12月-04日)</t>
+        </is>
+      </c>
+      <c r="D24" s="21" t="inlineStr">
         <is>
           <t>C | 290呎 (1房)
 $649万
 $22,372/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E24" s="22" t="inlineStr">
+(24年-04月-09日)</t>
+        </is>
+      </c>
+      <c r="E24" s="21" t="inlineStr">
         <is>
           <t>D | 266呎 (开放式)
 $656万
 $24,654/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="F24" s="22" t="inlineStr">
+(24年-11月-03日)</t>
+        </is>
+      </c>
+      <c r="F24" s="21" t="inlineStr">
         <is>
           <t>E | 266呎 (开放式)
 $472万
 $17,741/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="G24" s="22" t="inlineStr">
+(25年-11月-26日)</t>
+        </is>
+      </c>
+      <c r="G24" s="21" t="inlineStr">
         <is>
           <t>F | 292呎 (1房)
 $670万
 $22,942/呎
-(24年-03月)</t>
-        </is>
-      </c>
-      <c r="H24" s="22" t="inlineStr">
+(24年-03月-06日)</t>
+        </is>
+      </c>
+      <c r="H24" s="21" t="inlineStr">
         <is>
           <t>G | 293呎 (1房)
 $672万
 $22,942/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="I24" s="22" t="inlineStr">
+(24年-04月-22日)</t>
+        </is>
+      </c>
+      <c r="I24" s="21" t="inlineStr">
         <is>
           <t>H | 232呎 (开放式)
 $537万
 $23,164/呎
-(23年-07月)</t>
+(23年-07月-05日)</t>
         </is>
       </c>
     </row>
@@ -9532,68 +12128,68 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B25" s="22" t="inlineStr">
+      <c r="B25" s="21" t="inlineStr">
         <is>
           <t>A | 232呎 (开放式)
 $416万
 $17,931/呎
-(22年-11月)</t>
-        </is>
-      </c>
-      <c r="C25" s="22" t="inlineStr">
+(22年-11月-29日)</t>
+        </is>
+      </c>
+      <c r="C25" s="21" t="inlineStr">
         <is>
           <t>B | 401呎 (2房)
 $737万
 $18,389/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="D25" s="22" t="inlineStr">
+(26年-01月-26日)</t>
+        </is>
+      </c>
+      <c r="D25" s="21" t="inlineStr">
         <is>
           <t>C | 290呎 (1房)
 $626万
 $21,583/呎
-(23年-03月)</t>
-        </is>
-      </c>
-      <c r="E25" s="22" t="inlineStr">
+(23年-03月-23日)</t>
+        </is>
+      </c>
+      <c r="E25" s="21" t="inlineStr">
         <is>
           <t>D | 266呎 (开放式)
 $649万
 $24,414/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F25" s="22" t="inlineStr">
+(24年-05月-30日)</t>
+        </is>
+      </c>
+      <c r="F25" s="21" t="inlineStr">
         <is>
           <t>E | 266呎 (开放式)
 $659万
 $24,782/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="G25" s="22" t="inlineStr">
+(25年-02月-13日)</t>
+        </is>
+      </c>
+      <c r="G25" s="21" t="inlineStr">
         <is>
           <t>F | 292呎 (1房)
 $686万
 $23,476/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="H25" s="22" t="inlineStr">
+(25年-03月-02日)</t>
+        </is>
+      </c>
+      <c r="H25" s="21" t="inlineStr">
         <is>
           <t>G | 293呎 (1房)
 $559万
 $19,092/呎
-(22年-11月)</t>
-        </is>
-      </c>
-      <c r="I25" s="22" t="inlineStr">
+(22年-11月-29日)</t>
+        </is>
+      </c>
+      <c r="I25" s="21" t="inlineStr">
         <is>
           <t>H | 232呎 (开放式)
 $520万
 $22,422/呎
-(24年-03月)</t>
+(24年-03月-26日)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-长沙湾-连方I.xlsx
+++ b/files/九龙-长沙湾-连方I.xlsx
@@ -116,12 +116,12 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
+      <color rgb="007F7F7F"/>
       <sz val="8"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
+      <color rgb="00660000"/>
       <sz val="8"/>
     </font>
     <font>
@@ -266,13 +266,13 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1917,18 +1917,18 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>36%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="K20" s="5" t="n">
-        <v>5111680</v>
+        <v>6389600</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>19217</v>
+        <v>24021</v>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>120天即供付款計劃（照售價減5.5%）</t>
+          <t>120天即供付款計劃（照售價減3.5%）</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
@@ -2049,18 +2049,18 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>36%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="K22" s="5" t="n">
-        <v>5439360</v>
+        <v>6799200</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>18756</v>
+        <v>23446</v>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>120天即供付款計劃（照售價減5.5%）</t>
+          <t>120天即供付款計劃（照售價減3.5%）</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
@@ -2421,18 +2421,18 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>36%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="K28" s="5" t="n">
-        <v>5011840</v>
+        <v>6264800</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>18842</v>
+        <v>23552</v>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>120天即供付款計劃（照售價減5.5%）</t>
+          <t>120天即供付款計劃（照售價減3.5%）</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
@@ -2483,18 +2483,18 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>36%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="K29" s="5" t="n">
-        <v>5011840</v>
+        <v>6264800</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>18842</v>
+        <v>23552</v>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>120天即供付款計劃（照售價減5.5%）</t>
+          <t>120天即供付款計劃（照售價減3.5%）</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
@@ -2545,18 +2545,18 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>36%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="K30" s="5" t="n">
-        <v>5333120</v>
+        <v>6666400</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>18390</v>
+        <v>22988</v>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>120天即供付款計劃（照售價減5.5%）</t>
+          <t>120天即供付款計劃（照售價減3.5%）</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
@@ -2917,18 +2917,18 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>36%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="K36" s="5" t="n">
-        <v>4912640</v>
+        <v>6140800</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>18469</v>
+        <v>23086</v>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>120天即供付款計劃（照售價減5.5%）</t>
+          <t>120天即供付款計劃（照售價減3.5%）</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
@@ -2979,18 +2979,18 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>36%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="K37" s="5" t="n">
-        <v>4913280</v>
+        <v>6141600</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>18471</v>
+        <v>23089</v>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>120天即供付款計劃（照售價減5.5%）</t>
+          <t>120天即供付款計劃（照售價減3.5%）</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
@@ -3413,18 +3413,18 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>36%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="K44" s="5" t="n">
-        <v>4864640</v>
+        <v>6080800</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>18288</v>
+        <v>22860</v>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>120天即供付款計劃（照售價減5.5%）</t>
+          <t>120天即供付款計劃（照售價減3.5%）</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
@@ -3475,18 +3475,18 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>36%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="K45" s="5" t="n">
-        <v>4865280</v>
+        <v>6081600</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>18291</v>
+        <v>22863</v>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>120天即供付款計劃（照售價減5.5%）</t>
+          <t>120天即供付款計劃（照售價減3.5%）</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
@@ -7629,18 +7629,18 @@
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
-          <t>36%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K112" s="5" t="n">
-        <v>3477760</v>
+        <v>5352490</v>
       </c>
       <c r="L112" s="5" t="n">
-        <v>14990</v>
+        <v>23071</v>
       </c>
       <c r="M112" s="3" t="inlineStr">
         <is>
-          <t>120天即供付款計劃（照售價減5.5%）</t>
+          <t>120天即供付款計劃（照售價加3.5%）</t>
         </is>
       </c>
       <c r="N112" s="3" t="inlineStr">
@@ -10775,11 +10775,40 @@
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="19" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 547呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr"/>
+      <c r="D5" s="21" t="inlineStr"/>
+      <c r="E5" s="21" t="inlineStr"/>
+      <c r="F5" s="21" t="inlineStr"/>
+      <c r="G5" s="20" t="inlineStr">
+        <is>
+          <t>F | 439呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H5" s="21" t="inlineStr"/>
+      <c r="I5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
           <t>27&amp;28</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr"/>
-      <c r="C5" s="21" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t>B | 525呎 (2房)
 $1150万
@@ -10787,7 +10816,7 @@
 (25年-05月-07日)</t>
         </is>
       </c>
-      <c r="D5" s="22" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>C | 411呎 (1房)
 -
@@ -10795,7 +10824,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E5" s="22" t="inlineStr">
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>D | 411呎 (1房)
 -
@@ -10803,7 +10832,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F5" s="22" t="inlineStr">
+      <c r="F6" s="20" t="inlineStr">
         <is>
           <t>E | 525呎 (2房)
 -
@@ -10811,38 +10840,9 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G5" s="20" t="inlineStr"/>
-      <c r="H5" s="20" t="inlineStr"/>
-      <c r="I5" s="20" t="inlineStr"/>
-    </row>
-    <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B6" s="22" t="inlineStr">
-        <is>
-          <t>A | 547呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
-      <c r="E6" s="20" t="inlineStr"/>
-      <c r="F6" s="20" t="inlineStr"/>
-      <c r="G6" s="22" t="inlineStr">
-        <is>
-          <t>F | 439呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="H6" s="20" t="inlineStr"/>
-      <c r="I6" s="20" t="inlineStr"/>
+      <c r="G6" s="21" t="inlineStr"/>
+      <c r="H6" s="21" t="inlineStr"/>
+      <c r="I6" s="21" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
@@ -10850,7 +10850,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>A | 231呎 (开放式)
 $478万
@@ -10858,7 +10858,7 @@
 (26年-01月-25日)</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>B | 401呎 (2房)
 $1088万
@@ -10866,7 +10866,7 @@
 (24年-04月-16日)</t>
         </is>
       </c>
-      <c r="D7" s="22" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 290呎 (1房)
 -
@@ -10874,7 +10874,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E7" s="22" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>D | 266呎 (开放式)
 -
@@ -10882,7 +10882,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F7" s="22" t="inlineStr">
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>E | 266呎 (开放式)
 -
@@ -10890,7 +10890,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G7" s="22" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>F | 292呎 (1房)
 -
@@ -10898,7 +10898,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H7" s="22" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>G | 293呎 (1房)
 -
@@ -10906,7 +10906,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I7" s="21" t="inlineStr">
+      <c r="I7" s="22" t="inlineStr">
         <is>
           <t>H | 233呎 (开放式)
 $677万
@@ -10921,7 +10921,7 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>A | 231呎 (开放式)
 $473万
@@ -10929,7 +10929,7 @@
 (26年-01月-22日)</t>
         </is>
       </c>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t>B | 401呎 (2房)
 $1072万
@@ -10945,7 +10945,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E8" s="22" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t>D | 266呎 (开放式)
 -
@@ -10961,7 +10961,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G8" s="21" t="inlineStr">
+      <c r="G8" s="22" t="inlineStr">
         <is>
           <t>F | 292呎 (1房)
 $589万
@@ -10969,7 +10969,7 @@
 (26年-02月-12日)</t>
         </is>
       </c>
-      <c r="H8" s="21" t="inlineStr">
+      <c r="H8" s="22" t="inlineStr">
         <is>
           <t>G | 293呎 (1房)
 $660万
@@ -10977,7 +10977,7 @@
 (26年-02月-11日)</t>
         </is>
       </c>
-      <c r="I8" s="21" t="inlineStr">
+      <c r="I8" s="22" t="inlineStr">
         <is>
           <t>H | 233呎 (开放式)
 $458万
@@ -10992,7 +10992,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B9" s="21" t="inlineStr">
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>A | 231呎 (开放式)
 $655万
@@ -11000,7 +11000,7 @@
 (25年-06月-16日)</t>
         </is>
       </c>
-      <c r="C9" s="21" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>B | 401呎 (2房)
 $1056万
@@ -11032,7 +11032,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G9" s="21" t="inlineStr">
+      <c r="G9" s="22" t="inlineStr">
         <is>
           <t>F | 292呎 (1房)
 $577万
@@ -11040,7 +11040,7 @@
 (26年-02月-12日)</t>
         </is>
       </c>
-      <c r="H9" s="21" t="inlineStr">
+      <c r="H9" s="22" t="inlineStr">
         <is>
           <t>G | 293呎 (1房)
 $625万
@@ -11048,7 +11048,7 @@
 (25年-07月-28日)</t>
         </is>
       </c>
-      <c r="I9" s="21" t="inlineStr">
+      <c r="I9" s="22" t="inlineStr">
         <is>
           <t>H | 233呎 (开放式)
 $594万
@@ -11063,7 +11063,7 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B10" s="21" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>A | 231呎 (开放式)
 $458万
@@ -11071,7 +11071,7 @@
 (26年-01月-06日)</t>
         </is>
       </c>
-      <c r="C10" s="21" t="inlineStr">
+      <c r="C10" s="22" t="inlineStr">
         <is>
           <t>B | 401呎 (2房)
 $1040万
@@ -11079,7 +11079,7 @@
 (24年-04月-10日)</t>
         </is>
       </c>
-      <c r="D10" s="21" t="inlineStr">
+      <c r="D10" s="22" t="inlineStr">
         <is>
           <t>C | 290呎 (1房)
 $564万
@@ -11103,7 +11103,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G10" s="21" t="inlineStr">
+      <c r="G10" s="22" t="inlineStr">
         <is>
           <t>F | 292呎 (1房)
 $792万
@@ -11111,7 +11111,7 @@
 (25年-03月-09日)</t>
         </is>
       </c>
-      <c r="H10" s="21" t="inlineStr">
+      <c r="H10" s="22" t="inlineStr">
         <is>
           <t>G | 293呎 (1房)
 $905万
@@ -11119,7 +11119,7 @@
 (25年-05月-12日)</t>
         </is>
       </c>
-      <c r="I10" s="21" t="inlineStr">
+      <c r="I10" s="22" t="inlineStr">
         <is>
           <t>H | 232呎 (开放式)
 $649万
@@ -11134,7 +11134,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B11" s="21" t="inlineStr">
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>A | 231呎 (开放式)
 $454万
@@ -11142,7 +11142,7 @@
 (26年-01月-12日)</t>
         </is>
       </c>
-      <c r="C11" s="21" t="inlineStr">
+      <c r="C11" s="22" t="inlineStr">
         <is>
           <t>B | 401呎 (2房)
 $1025万
@@ -11150,7 +11150,7 @@
 (24年-04月-08日)</t>
         </is>
       </c>
-      <c r="D11" s="21" t="inlineStr">
+      <c r="D11" s="22" t="inlineStr">
         <is>
           <t>C | 290呎 (1房)
 $559万
@@ -11174,7 +11174,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G11" s="21" t="inlineStr">
+      <c r="G11" s="22" t="inlineStr">
         <is>
           <t>F | 292呎 (1房)
 $561万
@@ -11182,7 +11182,7 @@
 (26年-01月-22日)</t>
         </is>
       </c>
-      <c r="H11" s="21" t="inlineStr">
+      <c r="H11" s="22" t="inlineStr">
         <is>
           <t>G | 293呎 (1房)
 $830万
@@ -11190,7 +11190,7 @@
 (24年-11月-26日)</t>
         </is>
       </c>
-      <c r="I11" s="21" t="inlineStr">
+      <c r="I11" s="22" t="inlineStr">
         <is>
           <t>H | 233呎 (开放式)
 $642万
@@ -11205,7 +11205,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B12" s="21" t="inlineStr">
+      <c r="B12" s="22" t="inlineStr">
         <is>
           <t>A | 231呎 (开放式)
 $430万
@@ -11213,7 +11213,7 @@
 (25年-07月-29日)</t>
         </is>
       </c>
-      <c r="C12" s="21" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t>B | 401呎 (2房)
 $1010万
@@ -11221,7 +11221,7 @@
 (24年-04月-01日)</t>
         </is>
       </c>
-      <c r="D12" s="21" t="inlineStr">
+      <c r="D12" s="22" t="inlineStr">
         <is>
           <t>C | 290呎 (1房)
 $553万
@@ -11229,7 +11229,7 @@
 (25年-12月-15日)</t>
         </is>
       </c>
-      <c r="E12" s="21" t="inlineStr">
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t>D | 266呎 (开放式)
 $602万
@@ -11237,7 +11237,7 @@
 (26年-04月-19日)</t>
         </is>
       </c>
-      <c r="F12" s="21" t="inlineStr">
+      <c r="F12" s="22" t="inlineStr">
         <is>
           <t>E | 266呎 (开放式)
 $517万
@@ -11245,7 +11245,7 @@
 (26年-02月-04日)</t>
         </is>
       </c>
-      <c r="G12" s="21" t="inlineStr">
+      <c r="G12" s="22" t="inlineStr">
         <is>
           <t>F | 292呎 (1房)
 $532万
@@ -11253,7 +11253,7 @@
 (25年-08月-18日)</t>
         </is>
       </c>
-      <c r="H12" s="21" t="inlineStr">
+      <c r="H12" s="22" t="inlineStr">
         <is>
           <t>G | 293呎 (1房)
 $822万
@@ -11261,7 +11261,7 @@
 (24年-11月-18日)</t>
         </is>
       </c>
-      <c r="I12" s="21" t="inlineStr">
+      <c r="I12" s="22" t="inlineStr">
         <is>
           <t>H | 233呎 (开放式)
 $623万
@@ -11276,7 +11276,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B13" s="21" t="inlineStr">
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>A | 232呎 (开放式)
 $613万
@@ -11284,7 +11284,7 @@
 (24年-12月-11日)</t>
         </is>
       </c>
-      <c r="C13" s="21" t="inlineStr">
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t>B | 401呎 (2房)
 $1045万
@@ -11292,7 +11292,7 @@
 (25年-01月-02日)</t>
         </is>
       </c>
-      <c r="D13" s="21" t="inlineStr">
+      <c r="D13" s="22" t="inlineStr">
         <is>
           <t>C | 290呎 (1房)
 $737万
@@ -11300,7 +11300,7 @@
 (24年-04月-22日)</t>
         </is>
       </c>
-      <c r="E13" s="21" t="inlineStr">
+      <c r="E13" s="22" t="inlineStr">
         <is>
           <t>D | 266呎 (开放式)
 $516万
@@ -11308,7 +11308,7 @@
 (26年-01月-15日)</t>
         </is>
       </c>
-      <c r="F13" s="21" t="inlineStr">
+      <c r="F13" s="22" t="inlineStr">
         <is>
           <t>E | 266呎 (开放式)
 $514万
@@ -11316,7 +11316,7 @@
 (26年-03月-02日)</t>
         </is>
       </c>
-      <c r="G13" s="21" t="inlineStr">
+      <c r="G13" s="22" t="inlineStr">
         <is>
           <t>F | 292呎 (1房)
 $772万
@@ -11324,7 +11324,7 @@
 (24年-12月-11日)</t>
         </is>
       </c>
-      <c r="H13" s="21" t="inlineStr">
+      <c r="H13" s="22" t="inlineStr">
         <is>
           <t>G | 293呎 (1房)
 $789万
@@ -11332,7 +11332,7 @@
 (24年-06月-02日)</t>
         </is>
       </c>
-      <c r="I13" s="21" t="inlineStr">
+      <c r="I13" s="22" t="inlineStr">
         <is>
           <t>H | 233呎 (开放式)
 $617万
@@ -11347,7 +11347,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B14" s="21" t="inlineStr">
+      <c r="B14" s="22" t="inlineStr">
         <is>
           <t>A | 232呎 (开放式)
 $445万
@@ -11355,7 +11355,7 @@
 (25年-12月-16日)</t>
         </is>
       </c>
-      <c r="C14" s="21" t="inlineStr">
+      <c r="C14" s="22" t="inlineStr">
         <is>
           <t>B | 401呎 (2房)
 $995万
@@ -11363,7 +11363,7 @@
 (24年-03月-26日)</t>
         </is>
       </c>
-      <c r="D14" s="21" t="inlineStr">
+      <c r="D14" s="22" t="inlineStr">
         <is>
           <t>C | 290呎 (1房)
 $764万
@@ -11371,7 +11371,7 @@
 (24年-12月-05日)</t>
         </is>
       </c>
-      <c r="E14" s="21" t="inlineStr">
+      <c r="E14" s="22" t="inlineStr">
         <is>
           <t>D | 266呎 (开放式)
 $514万
@@ -11379,7 +11379,7 @@
 (25年-11月-26日)</t>
         </is>
       </c>
-      <c r="F14" s="21" t="inlineStr">
+      <c r="F14" s="22" t="inlineStr">
         <is>
           <t>E | 266呎 (开放式)
 $718万
@@ -11387,7 +11387,7 @@
 (24年-05月-08日)</t>
         </is>
       </c>
-      <c r="G14" s="21" t="inlineStr">
+      <c r="G14" s="22" t="inlineStr">
         <is>
           <t>F | 292呎 (1房)
 $551万
@@ -11395,7 +11395,7 @@
 (26年-02月-01日)</t>
         </is>
       </c>
-      <c r="H14" s="21" t="inlineStr">
+      <c r="H14" s="22" t="inlineStr">
         <is>
           <t>G | 293呎 (1房)
 $782万
@@ -11403,7 +11403,7 @@
 (24年-11月-12日)</t>
         </is>
       </c>
-      <c r="I14" s="21" t="inlineStr">
+      <c r="I14" s="22" t="inlineStr">
         <is>
           <t>H | 232呎 (开放式)
 $617万
@@ -11418,7 +11418,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B15" s="21" t="inlineStr">
+      <c r="B15" s="22" t="inlineStr">
         <is>
           <t>A | 232呎 (开放式)
 $594万
@@ -11426,7 +11426,7 @@
 (24年-05月-13日)</t>
         </is>
       </c>
-      <c r="C15" s="21" t="inlineStr">
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t>B | 401呎 (2房)
 $1034万
@@ -11434,7 +11434,7 @@
 (25年-02月-06日)</t>
         </is>
       </c>
-      <c r="D15" s="21" t="inlineStr">
+      <c r="D15" s="22" t="inlineStr">
         <is>
           <t>C | 290呎 (1房)
 $564万
@@ -11442,7 +11442,7 @@
 (26年-02月-15日)</t>
         </is>
       </c>
-      <c r="E15" s="21" t="inlineStr">
+      <c r="E15" s="22" t="inlineStr">
         <is>
           <t>D | 266呎 (开放式)
 $512万
@@ -11450,7 +11450,7 @@
 (26年-02月-08日)</t>
         </is>
       </c>
-      <c r="F15" s="21" t="inlineStr">
+      <c r="F15" s="22" t="inlineStr">
         <is>
           <t>E | 266呎 (开放式)
 $704万
@@ -11458,7 +11458,7 @@
 (24年-05月-20日)</t>
         </is>
       </c>
-      <c r="G15" s="21" t="inlineStr">
+      <c r="G15" s="22" t="inlineStr">
         <is>
           <t>F | 292呎 (1房)
 $763万
@@ -11466,7 +11466,7 @@
 (25年-01月-05日)</t>
         </is>
       </c>
-      <c r="H15" s="21" t="inlineStr">
+      <c r="H15" s="22" t="inlineStr">
         <is>
           <t>G | 293呎 (1房)
 $774万
@@ -11474,7 +11474,7 @@
 (24年-11月-19日)</t>
         </is>
       </c>
-      <c r="I15" s="21" t="inlineStr">
+      <c r="I15" s="22" t="inlineStr">
         <is>
           <t>H | 233呎 (开放式)
 $612万
@@ -11489,7 +11489,7 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B16" s="21" t="inlineStr">
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>A | 232呎 (开放式)
 $588万
@@ -11497,7 +11497,7 @@
 (24年-04月-16日)</t>
         </is>
       </c>
-      <c r="C16" s="21" t="inlineStr">
+      <c r="C16" s="22" t="inlineStr">
         <is>
           <t>B | 401呎 (2房)
 $1040万
@@ -11505,7 +11505,7 @@
 (25年-03月-06日)</t>
         </is>
       </c>
-      <c r="D16" s="21" t="inlineStr">
+      <c r="D16" s="22" t="inlineStr">
         <is>
           <t>C | 290呎 (1房)
 $753万
@@ -11513,7 +11513,7 @@
 (24年-11月-21日)</t>
         </is>
       </c>
-      <c r="E16" s="21" t="inlineStr">
+      <c r="E16" s="22" t="inlineStr">
         <is>
           <t>D | 266呎 (开放式)
 $712万
@@ -11521,7 +11521,7 @@
 (24年-12月-17日)</t>
         </is>
       </c>
-      <c r="F16" s="21" t="inlineStr">
+      <c r="F16" s="22" t="inlineStr">
         <is>
           <t>E | 266呎 (开放式)
 $687万
@@ -11529,7 +11529,7 @@
 (24年-04月-25日)</t>
         </is>
       </c>
-      <c r="G16" s="21" t="inlineStr">
+      <c r="G16" s="22" t="inlineStr">
         <is>
           <t>F | 292呎 (1房)
 $750万
@@ -11537,7 +11537,7 @@
 (24年-12月-17日)</t>
         </is>
       </c>
-      <c r="H16" s="21" t="inlineStr">
+      <c r="H16" s="22" t="inlineStr">
         <is>
           <t>G | 293呎 (1房)
 $770万
@@ -11545,7 +11545,7 @@
 (24年-09月-24日)</t>
         </is>
       </c>
-      <c r="I16" s="21" t="inlineStr">
+      <c r="I16" s="22" t="inlineStr">
         <is>
           <t>H | 232呎 (开放式)
 $606万
@@ -11560,7 +11560,7 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B17" s="21" t="inlineStr">
+      <c r="B17" s="22" t="inlineStr">
         <is>
           <t>A | 232呎 (开放式)
 $570万
@@ -11568,7 +11568,7 @@
 (24年-04月-17日)</t>
         </is>
       </c>
-      <c r="C17" s="21" t="inlineStr">
+      <c r="C17" s="22" t="inlineStr">
         <is>
           <t>B | 401呎 (2房)
 $1034万
@@ -11576,7 +11576,7 @@
 (25年-03月-27日)</t>
         </is>
       </c>
-      <c r="D17" s="21" t="inlineStr">
+      <c r="D17" s="22" t="inlineStr">
         <is>
           <t>C | 290呎 (1房)
 $748万
@@ -11584,7 +11584,7 @@
 (24年-11月-21日)</t>
         </is>
       </c>
-      <c r="E17" s="21" t="inlineStr">
+      <c r="E17" s="22" t="inlineStr">
         <is>
           <t>D | 266呎 (开放式)
 $719万
@@ -11592,7 +11592,7 @@
 (24年-11月-21日)</t>
         </is>
       </c>
-      <c r="F17" s="21" t="inlineStr">
+      <c r="F17" s="22" t="inlineStr">
         <is>
           <t>E | 266呎 (开放式)
 $682万
@@ -11600,7 +11600,7 @@
 (24年-05月-19日)</t>
         </is>
       </c>
-      <c r="G17" s="21" t="inlineStr">
+      <c r="G17" s="22" t="inlineStr">
         <is>
           <t>F | 292呎 (1房)
 $719万
@@ -11608,7 +11608,7 @@
 (24年-05月-08日)</t>
         </is>
       </c>
-      <c r="H17" s="21" t="inlineStr">
+      <c r="H17" s="22" t="inlineStr">
         <is>
           <t>G | 293呎 (1房)
 $766万
@@ -11616,7 +11616,7 @@
 (24年-06月-10日)</t>
         </is>
       </c>
-      <c r="I17" s="21" t="inlineStr">
+      <c r="I17" s="22" t="inlineStr">
         <is>
           <t>H | 233呎 (开放式)
 $588万
@@ -11631,7 +11631,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B18" s="21" t="inlineStr">
+      <c r="B18" s="22" t="inlineStr">
         <is>
           <t>A | 232呎 (开放式)
 $538万
@@ -11639,7 +11639,7 @@
 (23年-04月-05日)</t>
         </is>
       </c>
-      <c r="C18" s="21" t="inlineStr">
+      <c r="C18" s="22" t="inlineStr">
         <is>
           <t>B | 401呎 (2房)
 $805万
@@ -11647,7 +11647,7 @@
 (22年-12月-01日)</t>
         </is>
       </c>
-      <c r="D18" s="21" t="inlineStr">
+      <c r="D18" s="22" t="inlineStr">
         <is>
           <t>C | 290呎 (1房)
 $746万
@@ -11655,7 +11655,7 @@
 (25年-05月-21日)</t>
         </is>
       </c>
-      <c r="E18" s="21" t="inlineStr">
+      <c r="E18" s="22" t="inlineStr">
         <is>
           <t>D | 266呎 (开放式)
 $698万
@@ -11663,7 +11663,7 @@
 (24年-07月-01日)</t>
         </is>
       </c>
-      <c r="F18" s="21" t="inlineStr">
+      <c r="F18" s="22" t="inlineStr">
         <is>
           <t>E | 266呎 (开放式)
 $677万
@@ -11671,7 +11671,7 @@
 (24年-05月-13日)</t>
         </is>
       </c>
-      <c r="G18" s="21" t="inlineStr">
+      <c r="G18" s="22" t="inlineStr">
         <is>
           <t>F | 292呎 (1房)
 $743万
@@ -11679,7 +11679,7 @@
 (24年-11月-21日)</t>
         </is>
       </c>
-      <c r="H18" s="21" t="inlineStr">
+      <c r="H18" s="22" t="inlineStr">
         <is>
           <t>G | 293呎 (1房)
 $730万
@@ -11687,7 +11687,7 @@
 (24年-04月-17日)</t>
         </is>
       </c>
-      <c r="I18" s="21" t="inlineStr">
+      <c r="I18" s="22" t="inlineStr">
         <is>
           <t>H | 232呎 (开放式)
 $577万
@@ -11710,7 +11710,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C19" s="21" t="inlineStr">
+      <c r="C19" s="22" t="inlineStr">
         <is>
           <t>B | 401呎 (2房)
 $789万
@@ -11718,7 +11718,7 @@
 (22年-12月-12日)</t>
         </is>
       </c>
-      <c r="D19" s="21" t="inlineStr">
+      <c r="D19" s="22" t="inlineStr">
         <is>
           <t>C | 290呎 (1房)
 $732万
@@ -11726,7 +11726,7 @@
 (24年-07月-01日)</t>
         </is>
       </c>
-      <c r="E19" s="21" t="inlineStr">
+      <c r="E19" s="22" t="inlineStr">
         <is>
           <t>D | 266呎 (开放式)
 $691万
@@ -11734,7 +11734,7 @@
 (24年-12月-23日)</t>
         </is>
       </c>
-      <c r="F19" s="21" t="inlineStr">
+      <c r="F19" s="22" t="inlineStr">
         <is>
           <t>E | 266呎 (开放式)
 $673万
@@ -11742,7 +11742,7 @@
 (24年-04月-17日)</t>
         </is>
       </c>
-      <c r="G19" s="21" t="inlineStr">
+      <c r="G19" s="22" t="inlineStr">
         <is>
           <t>F | 292呎 (1房)
 $741万
@@ -11750,7 +11750,7 @@
 (24年-12月-03日)</t>
         </is>
       </c>
-      <c r="H19" s="21" t="inlineStr">
+      <c r="H19" s="22" t="inlineStr">
         <is>
           <t>G | 293呎 (1房)
 $726万
@@ -11758,7 +11758,7 @@
 (24年-04月-25日)</t>
         </is>
       </c>
-      <c r="I19" s="21" t="inlineStr">
+      <c r="I19" s="22" t="inlineStr">
         <is>
           <t>H | 233呎 (开放式)
 $569万
@@ -11773,7 +11773,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B20" s="21" t="inlineStr">
+      <c r="B20" s="22" t="inlineStr">
         <is>
           <t>A | 231呎 (开放式)
 $528万
@@ -11781,7 +11781,7 @@
 (26年-06月-04日)</t>
         </is>
       </c>
-      <c r="C20" s="21" t="inlineStr">
+      <c r="C20" s="22" t="inlineStr">
         <is>
           <t>B | 401呎 (2房)
 $754万
@@ -11789,7 +11789,7 @@
 (22年-11月-29日)</t>
         </is>
       </c>
-      <c r="D20" s="21" t="inlineStr">
+      <c r="D20" s="22" t="inlineStr">
         <is>
           <t>C | 290呎 (1房)
 $684万
@@ -11797,7 +11797,7 @@
 (24年-05月-01日)</t>
         </is>
       </c>
-      <c r="E20" s="21" t="inlineStr">
+      <c r="E20" s="22" t="inlineStr">
         <is>
           <t>D | 266呎 (开放式)
 $684万
@@ -11805,7 +11805,7 @@
 (24年-11月-21日)</t>
         </is>
       </c>
-      <c r="F20" s="21" t="inlineStr">
+      <c r="F20" s="22" t="inlineStr">
         <is>
           <t>E | 266呎 (开放式)
 $510万
@@ -11813,7 +11813,7 @@
 (26年-02月-15日)</t>
         </is>
       </c>
-      <c r="G20" s="21" t="inlineStr">
+      <c r="G20" s="22" t="inlineStr">
         <is>
           <t>F | 292呎 (1房)
 $694万
@@ -11821,7 +11821,7 @@
 (24年-03月-25日)</t>
         </is>
       </c>
-      <c r="H20" s="21" t="inlineStr">
+      <c r="H20" s="22" t="inlineStr">
         <is>
           <t>G | 293呎 (1房)
 $703万
@@ -11829,7 +11829,7 @@
 (24年-04月-14日)</t>
         </is>
       </c>
-      <c r="I20" s="21" t="inlineStr">
+      <c r="I20" s="22" t="inlineStr">
         <is>
           <t>H | 233呎 (开放式)
 $561万
@@ -11844,7 +11844,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B21" s="21" t="inlineStr">
+      <c r="B21" s="22" t="inlineStr">
         <is>
           <t>A | 231呎 (开放式)
 $459万
@@ -11852,7 +11852,7 @@
 (26年-02月-05日)</t>
         </is>
       </c>
-      <c r="C21" s="21" t="inlineStr">
+      <c r="C21" s="22" t="inlineStr">
         <is>
           <t>B | 401呎 (2房)
 $885万
@@ -11860,7 +11860,7 @@
 (23年-02月-21日)</t>
         </is>
       </c>
-      <c r="D21" s="21" t="inlineStr">
+      <c r="D21" s="22" t="inlineStr">
         <is>
           <t>C | 290呎 (1房)
 $673万
@@ -11868,7 +11868,7 @@
 (24年-04月-17日)</t>
         </is>
       </c>
-      <c r="E21" s="21" t="inlineStr">
+      <c r="E21" s="22" t="inlineStr">
         <is>
           <t>D | 266呎 (开放式)
 $677万
@@ -11876,7 +11876,7 @@
 (24年-11月-18日)</t>
         </is>
       </c>
-      <c r="F21" s="21" t="inlineStr">
+      <c r="F21" s="22" t="inlineStr">
         <is>
           <t>E | 266呎 (开放式)
 $648万
@@ -11884,7 +11884,7 @@
 (24年-04月-17日)</t>
         </is>
       </c>
-      <c r="G21" s="21" t="inlineStr">
+      <c r="G21" s="22" t="inlineStr">
         <is>
           <t>F | 292呎 (1房)
 $544万
@@ -11892,7 +11892,7 @@
 (26年-02月-12日)</t>
         </is>
       </c>
-      <c r="H21" s="21" t="inlineStr">
+      <c r="H21" s="22" t="inlineStr">
         <is>
           <t>G | 293呎 (1房)
 $696万
@@ -11900,7 +11900,7 @@
 (24年-04月-02日)</t>
         </is>
       </c>
-      <c r="I21" s="21" t="inlineStr">
+      <c r="I21" s="22" t="inlineStr">
         <is>
           <t>H | 233呎 (开放式)
 $560万
@@ -11915,7 +11915,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B22" s="21" t="inlineStr">
+      <c r="B22" s="22" t="inlineStr">
         <is>
           <t>A | 232呎 (开放式)
 $508万
@@ -11923,7 +11923,7 @@
 (23年-02月-13日)</t>
         </is>
       </c>
-      <c r="C22" s="21" t="inlineStr">
+      <c r="C22" s="22" t="inlineStr">
         <is>
           <t>B | 401呎 (2房)
 $757万
@@ -11931,7 +11931,7 @@
 (22年-11月-29日)</t>
         </is>
       </c>
-      <c r="D22" s="21" t="inlineStr">
+      <c r="D22" s="22" t="inlineStr">
         <is>
           <t>C | 290呎 (1房)
 $666万
@@ -11939,7 +11939,7 @@
 (24年-04月-17日)</t>
         </is>
       </c>
-      <c r="E22" s="21" t="inlineStr">
+      <c r="E22" s="22" t="inlineStr">
         <is>
           <t>D | 266呎 (开放式)
 $674万
@@ -11947,7 +11947,7 @@
 (24年-07月-21日)</t>
         </is>
       </c>
-      <c r="F22" s="21" t="inlineStr">
+      <c r="F22" s="22" t="inlineStr">
         <is>
           <t>E | 266呎 (开放式)
 $508万
@@ -11955,7 +11955,7 @@
 (26年-02月-24日)</t>
         </is>
       </c>
-      <c r="G22" s="21" t="inlineStr">
+      <c r="G22" s="22" t="inlineStr">
         <is>
           <t>F | 292呎 (1房)
 $668万
@@ -11963,7 +11963,7 @@
 (23年-03月-27日)</t>
         </is>
       </c>
-      <c r="H22" s="21" t="inlineStr">
+      <c r="H22" s="22" t="inlineStr">
         <is>
           <t>G | 293呎 (1房)
 $700万
@@ -11971,7 +11971,7 @@
 (24年-03月-09日)</t>
         </is>
       </c>
-      <c r="I22" s="21" t="inlineStr">
+      <c r="I22" s="22" t="inlineStr">
         <is>
           <t>H | 232呎 (开放式)
 $556万
@@ -11986,7 +11986,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B23" s="21" t="inlineStr">
+      <c r="B23" s="22" t="inlineStr">
         <is>
           <t>A | 231呎 (开放式)
 $443万
@@ -11994,7 +11994,7 @@
 (26年-01月-26日)</t>
         </is>
       </c>
-      <c r="C23" s="21" t="inlineStr">
+      <c r="C23" s="22" t="inlineStr">
         <is>
           <t>B | 401呎 (2房)
 $860万
@@ -12002,7 +12002,7 @@
 (23年-02月-23日)</t>
         </is>
       </c>
-      <c r="D23" s="21" t="inlineStr">
+      <c r="D23" s="22" t="inlineStr">
         <is>
           <t>C | 290呎 (1房)
 $656万
@@ -12010,7 +12010,7 @@
 (24年-04月-09日)</t>
         </is>
       </c>
-      <c r="E23" s="21" t="inlineStr">
+      <c r="E23" s="22" t="inlineStr">
         <is>
           <t>D | 266呎 (开放式)
 $662万
@@ -12018,7 +12018,7 @@
 (24年-12月-11日)</t>
         </is>
       </c>
-      <c r="F23" s="21" t="inlineStr">
+      <c r="F23" s="22" t="inlineStr">
         <is>
           <t>E | 266呎 (开放式)
 $630万
@@ -12026,7 +12026,7 @@
 (24年-03月-26日)</t>
         </is>
       </c>
-      <c r="G23" s="21" t="inlineStr">
+      <c r="G23" s="22" t="inlineStr">
         <is>
           <t>F | 292呎 (1房)
 $668万
@@ -12034,7 +12034,7 @@
 (24年-04月-22日)</t>
         </is>
       </c>
-      <c r="H23" s="21" t="inlineStr">
+      <c r="H23" s="22" t="inlineStr">
         <is>
           <t>G | 293呎 (1房)
 $692万
@@ -12042,7 +12042,7 @@
 (24年-03月-20日)</t>
         </is>
       </c>
-      <c r="I23" s="21" t="inlineStr">
+      <c r="I23" s="22" t="inlineStr">
         <is>
           <t>H | 233呎 (开放式)
 $603万
@@ -12057,7 +12057,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B24" s="21" t="inlineStr">
+      <c r="B24" s="22" t="inlineStr">
         <is>
           <t>A | 231呎 (开放式)
 $440万
@@ -12065,7 +12065,7 @@
 (26年-01月-22日)</t>
         </is>
       </c>
-      <c r="C24" s="21" t="inlineStr">
+      <c r="C24" s="22" t="inlineStr">
         <is>
           <t>B | 401呎 (2房)
 $722万
@@ -12073,7 +12073,7 @@
 (22年-12月-04日)</t>
         </is>
       </c>
-      <c r="D24" s="21" t="inlineStr">
+      <c r="D24" s="22" t="inlineStr">
         <is>
           <t>C | 290呎 (1房)
 $649万
@@ -12081,7 +12081,7 @@
 (24年-04月-09日)</t>
         </is>
       </c>
-      <c r="E24" s="21" t="inlineStr">
+      <c r="E24" s="22" t="inlineStr">
         <is>
           <t>D | 266呎 (开放式)
 $656万
@@ -12089,7 +12089,7 @@
 (24年-11月-03日)</t>
         </is>
       </c>
-      <c r="F24" s="21" t="inlineStr">
+      <c r="F24" s="22" t="inlineStr">
         <is>
           <t>E | 266呎 (开放式)
 $472万
@@ -12097,7 +12097,7 @@
 (25年-11月-26日)</t>
         </is>
       </c>
-      <c r="G24" s="21" t="inlineStr">
+      <c r="G24" s="22" t="inlineStr">
         <is>
           <t>F | 292呎 (1房)
 $670万
@@ -12105,7 +12105,7 @@
 (24年-03月-06日)</t>
         </is>
       </c>
-      <c r="H24" s="21" t="inlineStr">
+      <c r="H24" s="22" t="inlineStr">
         <is>
           <t>G | 293呎 (1房)
 $672万
@@ -12113,7 +12113,7 @@
 (24年-04月-22日)</t>
         </is>
       </c>
-      <c r="I24" s="21" t="inlineStr">
+      <c r="I24" s="22" t="inlineStr">
         <is>
           <t>H | 232呎 (开放式)
 $537万
@@ -12128,7 +12128,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B25" s="21" t="inlineStr">
+      <c r="B25" s="22" t="inlineStr">
         <is>
           <t>A | 232呎 (开放式)
 $416万
@@ -12136,7 +12136,7 @@
 (22年-11月-29日)</t>
         </is>
       </c>
-      <c r="C25" s="21" t="inlineStr">
+      <c r="C25" s="22" t="inlineStr">
         <is>
           <t>B | 401呎 (2房)
 $737万
@@ -12144,7 +12144,7 @@
 (26年-01月-26日)</t>
         </is>
       </c>
-      <c r="D25" s="21" t="inlineStr">
+      <c r="D25" s="22" t="inlineStr">
         <is>
           <t>C | 290呎 (1房)
 $626万
@@ -12152,7 +12152,7 @@
 (23年-03月-23日)</t>
         </is>
       </c>
-      <c r="E25" s="21" t="inlineStr">
+      <c r="E25" s="22" t="inlineStr">
         <is>
           <t>D | 266呎 (开放式)
 $649万
@@ -12160,7 +12160,7 @@
 (24年-05月-30日)</t>
         </is>
       </c>
-      <c r="F25" s="21" t="inlineStr">
+      <c r="F25" s="22" t="inlineStr">
         <is>
           <t>E | 266呎 (开放式)
 $659万
@@ -12168,7 +12168,7 @@
 (25年-02月-13日)</t>
         </is>
       </c>
-      <c r="G25" s="21" t="inlineStr">
+      <c r="G25" s="22" t="inlineStr">
         <is>
           <t>F | 292呎 (1房)
 $686万
@@ -12176,7 +12176,7 @@
 (25年-03月-02日)</t>
         </is>
       </c>
-      <c r="H25" s="21" t="inlineStr">
+      <c r="H25" s="22" t="inlineStr">
         <is>
           <t>G | 293呎 (1房)
 $559万
@@ -12184,7 +12184,7 @@
 (22年-11月-29日)</t>
         </is>
       </c>
-      <c r="I25" s="21" t="inlineStr">
+      <c r="I25" s="22" t="inlineStr">
         <is>
           <t>H | 232呎 (开放式)
 $520万
